--- a/output/IMG_9688.xlsx
+++ b/output/IMG_9688.xlsx
@@ -41,21 +41,15 @@
       <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="14">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -100,6 +94,52 @@
     <border>
       <left style="medium"/>
       <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
@@ -116,6 +156,20 @@
       <bottom style="medium"/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
@@ -127,45 +181,27 @@
       <top style="thin"/>
       <bottom style="medium"/>
     </border>
-    <border>
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -176,46 +212,51 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -581,18 +622,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10.83333333333333" customWidth="1" min="1" max="1"/>
+    <col width="10.83333333333333" customWidth="1" min="2" max="2"/>
+    <col width="10.83333333333333" customWidth="1" min="3" max="3"/>
+    <col width="10.83333333333333" customWidth="1" min="4" max="4"/>
+    <col width="10.83333333333333" customWidth="1" min="5" max="5"/>
+    <col width="10.83333333333333" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>製造指図書</t>
@@ -603,6 +650,12 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -610,155 +663,185 @@
           <t>手配No.</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>0000056481</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>2018/12/05</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>手配先</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>S00000200 製造１課　倉庫</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>手配納期</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2018/12/14</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>作成者</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>品目CD</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>HA0002610</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>工順</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>発注手配数</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>400.72 kg</t>
         </is>
       </c>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>品目名</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>製番</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>0000051090</t>
         </is>
       </c>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>手配内容</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>20　　仕込</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>完成入庫</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>S00000200 製造１課　倉庫</t>
-        </is>
-      </c>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>S00000200　製造１課　倉庫</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ロットNo.</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="2" t="n"/>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>完成日</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
           <t>調合票</t>
@@ -768,361 +851,567 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>責任者</t>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>成分名</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>原単位</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>分量</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>秤量者</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>原料ロット</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>確認者</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>成分名</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>原単位</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>分量</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>秤量者</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>原料ロット</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>確認者</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="12" t="n"/>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>GE0006280　　　　999 購入
 Wheyco W80-パフォーマンスアカデミー</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>89.8383</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>360.00
 kg</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr"/>
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>GE0005150　　　　999 購入
 TATA INSTANT COFFEE FR-2132（深煎り）</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>5.9893</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="H12" s="19" t="inlineStr">
         <is>
           <t>24.00
 kg</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr"/>
+      <c r="J12" s="18" t="inlineStr"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>GE0004220　　　　999 購入
 練乳パウダー</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>2.2959</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="H13" s="19" t="inlineStr">
         <is>
           <t>9.20
 kg</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr"/>
+      <c r="J13" s="18" t="inlineStr"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>GE0003040　　　　999 購入
 ステラロース200（大宮糧食）</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>0.2795</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="H14" s="19" t="inlineStr">
         <is>
           <t>1.12
 kg</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr"/>
+      <c r="J14" s="18" t="inlineStr"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>GE0002070　　　　999 購入
-ソレックK-EML</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
+アレックK-EML</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>0.2995</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="H15" s="19" t="inlineStr">
         <is>
           <t>1.20
 kg</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr"/>
+      <c r="J15" s="18" t="inlineStr"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>GE0003110　　　　999 購入
-ポエムＺＬ－３</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
+ポエムZL－3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>0.4991</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="H16" s="19" t="inlineStr">
         <is>
           <t>2.00
 kg</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr"/>
-      <c r="E18" s="14" t="inlineStr"/>
-      <c r="F18" s="16" t="inlineStr"/>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr"/>
+      <c r="J16" s="18" t="inlineStr"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>GE0006810　　　　999 購入
-バタダートミルクコーヒー SSH-181</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
+バカダートミルクコーヒー SSH-181</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>0.4991</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="H17" s="19" t="inlineStr">
         <is>
           <t>2.00
 kg</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr"/>
-      <c r="E19" s="14" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr"/>
+      <c r="J17" s="18" t="inlineStr"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>GE0004800　　　　999 購入
 コーヒーパウダーフレーバー YM-5309</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>0.2995</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="H18" s="19" t="inlineStr">
         <is>
           <t>1.20
 kg</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr"/>
-      <c r="E20" s="14" t="inlineStr"/>
-      <c r="F20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
+      <c r="I18" s="18" t="inlineStr"/>
+      <c r="J18" s="18" t="inlineStr"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="21" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="21" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="23" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="21" t="n"/>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
-      <c r="F21" s="17" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="n"/>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="19" t="n"/>
-      <c r="F22" s="20" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="n"/>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="20" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="n"/>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="20" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="n"/>
-      <c r="B25" s="19" t="n"/>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="19" t="n"/>
-      <c r="F25" s="20" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="n"/>
-      <c r="B26" s="19" t="n"/>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="19" t="n"/>
-      <c r="E26" s="19" t="n"/>
-      <c r="F26" s="20" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="n"/>
-      <c r="B27" s="19" t="n"/>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="20" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="n"/>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="19" t="n"/>
-      <c r="F28" s="20" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="n"/>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="20" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="n"/>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="20" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="n"/>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="20" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="n"/>
-      <c r="B32" s="19" t="n"/>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="19" t="n"/>
-      <c r="F32" s="20" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="n"/>
-      <c r="B33" s="19" t="n"/>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="20" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="21" t="n"/>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="23" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="23" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="21" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="22" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="23" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="21" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="23" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="21" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="22" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="21" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="22" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="23" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="21" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="22" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="23" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="21" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="22" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="23" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="21" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="23" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="21" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="22" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="23" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="21" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="22" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="23" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="21" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="23" t="n"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="25" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="25" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="25" t="n"/>
+      <c r="L32" s="26" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="D10:D11"/>
+  <mergeCells count="75">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A9:F10"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="J13:K13"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J9:K10"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/IMG_9688.xlsx
+++ b/output/IMG_9688.xlsx
@@ -26,7 +26,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
@@ -185,20 +184,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -219,37 +212,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="right" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="right" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -622,21 +614,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.83333333333333" customWidth="1" min="1" max="1"/>
-    <col width="10.83333333333333" customWidth="1" min="2" max="2"/>
-    <col width="10.83333333333333" customWidth="1" min="3" max="3"/>
-    <col width="10.83333333333333" customWidth="1" min="4" max="4"/>
-    <col width="10.83333333333333" customWidth="1" min="5" max="5"/>
-    <col width="10.83333333333333" customWidth="1" min="6" max="6"/>
+    <col width="11.6" customWidth="1" min="1" max="1"/>
+    <col width="11.6" customWidth="1" min="2" max="2"/>
+    <col width="11.6" customWidth="1" min="3" max="3"/>
+    <col width="11.6" customWidth="1" min="4" max="4"/>
+    <col width="11.6" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1">
@@ -670,7 +662,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" s="3" t="inlineStr"/>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -698,7 +690,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>S00000200 製造１課　倉庫</t>
         </is>
@@ -728,7 +720,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>HA0002610</t>
         </is>
@@ -751,7 +743,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n"/>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>400.72 kg</t>
         </is>
@@ -766,9 +758,9 @@
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>グレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
@@ -796,7 +788,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>20　　仕込</t>
         </is>
@@ -811,9 +803,9 @@
         </is>
       </c>
       <c r="I6" s="2" t="n"/>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>S00000200　製造１課　倉庫</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>S00000200 製造１課　倉庫</t>
         </is>
       </c>
       <c r="K6" s="2" t="n"/>
@@ -826,7 +818,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -837,7 +829,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n"/>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
     </row>
@@ -860,280 +852,288 @@
       <c r="L8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>成分名</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>原単位</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>分量</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>秤量者</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>原料ロット</t>
         </is>
       </c>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
+      <c r="L9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n"/>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" s="11" t="n"/>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>GE0006280　　　　999 購入
-Wheyco W80-パフォーマンスアカデミー</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>GE0006280
+Wheyco W80-パフォーマンスアカデミー
+999 購入</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>89.8383</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>360.00
 kg</t>
         </is>
       </c>
+      <c r="H11" s="14" t="inlineStr"/>
       <c r="I11" s="14" t="inlineStr"/>
-      <c r="J11" s="14" t="inlineStr"/>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>GE0005150　　　　999 購入
-TATA INSTANT COFFEE FR-2132（深煎り）</t>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="14" t="inlineStr"/>
+      <c r="L11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>GE0005150
+TATA INSTANT COFFEE FR-2132（深煎り）
+999 購入</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>5.9893</t>
+        </is>
+      </c>
       <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>5.9893</t>
-        </is>
-      </c>
-      <c r="H12" s="19" t="inlineStr">
         <is>
           <t>24.00
 kg</t>
         </is>
       </c>
-      <c r="I12" s="18" t="inlineStr"/>
-      <c r="J12" s="18" t="inlineStr"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>GE0004220　　　　999 購入
-練乳パウダー</t>
+      <c r="H12" s="19" t="inlineStr"/>
+      <c r="I12" s="19" t="inlineStr"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="19" t="inlineStr"/>
+      <c r="L12" s="20" t="n"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>GE0004220
+練乳パウダー
+999 購入</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>2.2959</t>
+        </is>
+      </c>
       <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>2.2959</t>
-        </is>
-      </c>
-      <c r="H13" s="19" t="inlineStr">
         <is>
           <t>9.20
 kg</t>
         </is>
       </c>
-      <c r="I13" s="18" t="inlineStr"/>
-      <c r="J13" s="18" t="inlineStr"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="20" t="inlineStr"/>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>GE0003040　　　　999 購入
-ステラロース200（大宮糧食）</t>
+      <c r="H13" s="19" t="inlineStr"/>
+      <c r="I13" s="19" t="inlineStr"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="19" t="inlineStr"/>
+      <c r="L13" s="20" t="n"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>GE0003040
+ステラロース200（大宮糧食）
+999 購入</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>0.2795</t>
+        </is>
+      </c>
       <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>0.2795</t>
-        </is>
-      </c>
-      <c r="H14" s="19" t="inlineStr">
         <is>
           <t>1.12
 kg</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr"/>
-      <c r="J14" s="18" t="inlineStr"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="20" t="inlineStr"/>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>GE0002070　　　　999 購入
-アレックK-EML</t>
+      <c r="H14" s="19" t="inlineStr"/>
+      <c r="I14" s="19" t="inlineStr"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="19" t="inlineStr"/>
+      <c r="L14" s="20" t="n"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>GE0002070
+アレック K-EML
+999 購入</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>0.2995</t>
+        </is>
+      </c>
       <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>0.2995</t>
-        </is>
-      </c>
-      <c r="H15" s="19" t="inlineStr">
         <is>
           <t>1.20
 kg</t>
         </is>
       </c>
-      <c r="I15" s="18" t="inlineStr"/>
-      <c r="J15" s="18" t="inlineStr"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>GE0003110　　　　999 購入
-ポエムZL－3</t>
+      <c r="H15" s="19" t="inlineStr"/>
+      <c r="I15" s="19" t="inlineStr"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="19" t="inlineStr"/>
+      <c r="L15" s="20" t="n"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>GE0003110
+ポエムＺＬ－３
+999 購入</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>0.4991</t>
+        </is>
+      </c>
       <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>0.4991</t>
-        </is>
-      </c>
-      <c r="H16" s="19" t="inlineStr">
         <is>
           <t>2.00
 kg</t>
         </is>
       </c>
-      <c r="I16" s="18" t="inlineStr"/>
-      <c r="J16" s="18" t="inlineStr"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="20" t="inlineStr"/>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>GE0006810　　　　999 購入
-バカダートミルクコーヒー SSH-181</t>
+      <c r="H16" s="19" t="inlineStr"/>
+      <c r="I16" s="19" t="inlineStr"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="19" t="inlineStr"/>
+      <c r="L16" s="20" t="n"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>GE0006810
+バカダートミルクコーヒー SSH-181
+999 購入</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>0.4991</t>
+        </is>
+      </c>
       <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>0.4991</t>
-        </is>
-      </c>
-      <c r="H17" s="19" t="inlineStr">
         <is>
           <t>2.00
 kg</t>
         </is>
       </c>
-      <c r="I17" s="18" t="inlineStr"/>
-      <c r="J17" s="18" t="inlineStr"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="20" t="inlineStr"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>GE0004800　　　　999 購入
-コーヒーパウダーフレーバー YM-5309</t>
+      <c r="H17" s="19" t="inlineStr"/>
+      <c r="I17" s="19" t="inlineStr"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="19" t="inlineStr"/>
+      <c r="L17" s="20" t="n"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>GE0004800
+コーヒーパウダーフレーバー YM-5309
+999 購入</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>0.2995</t>
+        </is>
+      </c>
       <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>0.2995</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="inlineStr">
         <is>
           <t>1.20
 kg</t>
         </is>
       </c>
-      <c r="I18" s="18" t="inlineStr"/>
-      <c r="J18" s="18" t="inlineStr"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="20" t="inlineStr"/>
+      <c r="H18" s="19" t="inlineStr"/>
+      <c r="I18" s="19" t="inlineStr"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="19" t="inlineStr"/>
+      <c r="L18" s="20" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="21" t="n"/>
@@ -1141,13 +1141,13 @@
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
+      <c r="F19" s="22" t="n"/>
       <c r="G19" s="22" t="n"/>
       <c r="H19" s="22" t="n"/>
       <c r="I19" s="22" t="n"/>
-      <c r="J19" s="22" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="23" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="22" t="n"/>
+      <c r="L19" s="20" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="21" t="n"/>
@@ -1155,13 +1155,13 @@
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
+      <c r="F20" s="22" t="n"/>
       <c r="G20" s="22" t="n"/>
       <c r="H20" s="22" t="n"/>
       <c r="I20" s="22" t="n"/>
-      <c r="J20" s="22" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="23" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="20" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="21" t="n"/>
@@ -1169,13 +1169,13 @@
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
+      <c r="F21" s="22" t="n"/>
       <c r="G21" s="22" t="n"/>
       <c r="H21" s="22" t="n"/>
       <c r="I21" s="22" t="n"/>
-      <c r="J21" s="22" t="n"/>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="23" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="22" t="n"/>
+      <c r="L21" s="20" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="21" t="n"/>
@@ -1183,13 +1183,13 @@
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
+      <c r="F22" s="22" t="n"/>
       <c r="G22" s="22" t="n"/>
       <c r="H22" s="22" t="n"/>
       <c r="I22" s="22" t="n"/>
-      <c r="J22" s="22" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="23" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="22" t="n"/>
+      <c r="L22" s="20" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="21" t="n"/>
@@ -1197,13 +1197,13 @@
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
+      <c r="F23" s="22" t="n"/>
       <c r="G23" s="22" t="n"/>
       <c r="H23" s="22" t="n"/>
       <c r="I23" s="22" t="n"/>
-      <c r="J23" s="22" t="n"/>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="23" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="22" t="n"/>
+      <c r="L23" s="20" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="21" t="n"/>
@@ -1211,13 +1211,13 @@
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
+      <c r="F24" s="22" t="n"/>
       <c r="G24" s="22" t="n"/>
       <c r="H24" s="22" t="n"/>
       <c r="I24" s="22" t="n"/>
-      <c r="J24" s="22" t="n"/>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="23" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="22" t="n"/>
+      <c r="L24" s="20" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="21" t="n"/>
@@ -1225,13 +1225,13 @@
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
+      <c r="F25" s="22" t="n"/>
       <c r="G25" s="22" t="n"/>
       <c r="H25" s="22" t="n"/>
       <c r="I25" s="22" t="n"/>
-      <c r="J25" s="22" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="23" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="22" t="n"/>
+      <c r="L25" s="20" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="21" t="n"/>
@@ -1239,13 +1239,13 @@
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
+      <c r="F26" s="22" t="n"/>
       <c r="G26" s="22" t="n"/>
       <c r="H26" s="22" t="n"/>
       <c r="I26" s="22" t="n"/>
-      <c r="J26" s="22" t="n"/>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="23" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="22" t="n"/>
+      <c r="L26" s="20" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="21" t="n"/>
@@ -1253,13 +1253,13 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
+      <c r="F27" s="22" t="n"/>
       <c r="G27" s="22" t="n"/>
       <c r="H27" s="22" t="n"/>
       <c r="I27" s="22" t="n"/>
-      <c r="J27" s="22" t="n"/>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="23" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="22" t="n"/>
+      <c r="L27" s="20" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="21" t="n"/>
@@ -1267,13 +1267,13 @@
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
+      <c r="F28" s="22" t="n"/>
       <c r="G28" s="22" t="n"/>
       <c r="H28" s="22" t="n"/>
       <c r="I28" s="22" t="n"/>
-      <c r="J28" s="22" t="n"/>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="23" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="22" t="n"/>
+      <c r="L28" s="20" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="21" t="n"/>
@@ -1281,13 +1281,13 @@
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
+      <c r="F29" s="22" t="n"/>
       <c r="G29" s="22" t="n"/>
       <c r="H29" s="22" t="n"/>
       <c r="I29" s="22" t="n"/>
-      <c r="J29" s="22" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="23" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="22" t="n"/>
+      <c r="L29" s="20" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="21" t="n"/>
@@ -1295,13 +1295,13 @@
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
+      <c r="F30" s="22" t="n"/>
       <c r="G30" s="22" t="n"/>
       <c r="H30" s="22" t="n"/>
       <c r="I30" s="22" t="n"/>
-      <c r="J30" s="22" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="23" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="22" t="n"/>
+      <c r="L30" s="20" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="21" t="n"/>
@@ -1309,108 +1309,146 @@
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
+      <c r="F31" s="22" t="n"/>
       <c r="G31" s="22" t="n"/>
       <c r="H31" s="22" t="n"/>
       <c r="I31" s="22" t="n"/>
-      <c r="J31" s="22" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="23" t="n"/>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="22" t="n"/>
+      <c r="L31" s="20" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="21" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="22" t="n"/>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="22" t="n"/>
+      <c r="L32" s="20" t="n"/>
+    </row>
+    <row r="33" ht="150" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="25" t="n"/>
-      <c r="D32" s="25" t="n"/>
-      <c r="E32" s="25" t="n"/>
-      <c r="F32" s="25" t="n"/>
-      <c r="G32" s="25" t="n"/>
-      <c r="H32" s="25" t="n"/>
-      <c r="I32" s="25" t="n"/>
-      <c r="J32" s="25" t="n"/>
-      <c r="K32" s="25" t="n"/>
-      <c r="L32" s="26" t="n"/>
+      <c r="B33" s="24" t="n"/>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="24" t="n"/>
+      <c r="E33" s="24" t="n"/>
+      <c r="F33" s="24" t="n"/>
+      <c r="G33" s="24" t="n"/>
+      <c r="H33" s="24" t="n"/>
+      <c r="I33" s="24" t="n"/>
+      <c r="J33" s="24" t="n"/>
+      <c r="K33" s="24" t="n"/>
+      <c r="L33" s="25" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="75">
-    <mergeCell ref="A16:F16"/>
+  <mergeCells count="99">
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="K16:L16"/>
     <mergeCell ref="J6:L6"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A9:E10"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="C6:G6"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A9:F10"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="I27:J27"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="K20:L20"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
     <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="I12:J12"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="K12:L12"/>
     <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J9:K10"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="I31:J31"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/IMG_9688.xlsx
+++ b/output/IMG_9688.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,14 +26,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -184,58 +194,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,7 +251,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -617,12 +624,12 @@
   <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.6" customWidth="1" min="1" max="1"/>
-    <col width="11.6" customWidth="1" min="2" max="2"/>
-    <col width="11.6" customWidth="1" min="3" max="3"/>
-    <col width="11.6" customWidth="1" min="4" max="4"/>
-    <col width="11.6" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11.8" customWidth="1" min="1" max="1"/>
+    <col width="11.8" customWidth="1" min="2" max="2"/>
+    <col width="11.8" customWidth="1" min="3" max="3"/>
+    <col width="11.8" customWidth="1" min="4" max="4"/>
+    <col width="11.8" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -631,7 +638,7 @@
     <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="45" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>製造指図書</t>
@@ -649,7 +656,7 @@
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>手配No.</t>
@@ -662,28 +669,32 @@
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
           <t>発行日</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2018/12/05</t>
         </is>
       </c>
+      <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>作成者</t>
+        </is>
+      </c>
       <c r="L2" s="2" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>手配先</t>
@@ -713,7 +724,7 @@
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>品目CD</t>
@@ -751,7 +762,7 @@
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>品目名</t>
@@ -760,7 +771,7 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>グレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
+          <t>クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
@@ -781,7 +792,7 @@
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>手配内容</t>
@@ -811,7 +822,7 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ロットNo.</t>
@@ -833,8 +844,8 @@
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>調合票</t>
         </is>
@@ -848,96 +859,98 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>責任者</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>成分名</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>原単位</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>分量</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>秤量者</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>原料ロット</t>
         </is>
       </c>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
-      <c r="L9" s="6" t="n"/>
+      <c r="L9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>GE0006280
-Wheyco W80-パフォーマンスアカデミー
-999 購入</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>GE0006280  999 購入
+Wheyco W80-パフォーマンスアカデミー</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>89.8383</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>360.00
 kg</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="14" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="13" t="inlineStr"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="13" t="inlineStr"/>
       <c r="L11" s="15" t="n"/>
     </row>
-    <row r="12" ht="90" customHeight="1">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>GE0005150
-TATA INSTANT COFFEE FR-2132（深煎り）
-999 購入</t>
+          <t>GE0005150  999 購入
+TATA INSTANT COFFEE FR-2132（深煎り）</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -955,18 +968,17 @@
 kg</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr"/>
-      <c r="I12" s="19" t="inlineStr"/>
+      <c r="H12" s="17" t="inlineStr"/>
+      <c r="I12" s="17" t="inlineStr"/>
       <c r="J12" s="2" t="n"/>
-      <c r="K12" s="19" t="inlineStr"/>
-      <c r="L12" s="20" t="n"/>
-    </row>
-    <row r="13" ht="90" customHeight="1">
+      <c r="K12" s="17" t="inlineStr"/>
+      <c r="L12" s="19" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>GE0004220
-練乳パウダー
-999 購入</t>
+          <t>GE0004220  999 購入
+練乳パウダー</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -984,18 +996,17 @@
 kg</t>
         </is>
       </c>
-      <c r="H13" s="19" t="inlineStr"/>
-      <c r="I13" s="19" t="inlineStr"/>
+      <c r="H13" s="17" t="inlineStr"/>
+      <c r="I13" s="17" t="inlineStr"/>
       <c r="J13" s="2" t="n"/>
-      <c r="K13" s="19" t="inlineStr"/>
-      <c r="L13" s="20" t="n"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
+      <c r="K13" s="17" t="inlineStr"/>
+      <c r="L13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>GE0003040
-ステラロース200（大宮糧食）
-999 購入</t>
+          <t>GE0003040  999 購入
+ステラロース200（大宮糧食）</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -1013,18 +1024,17 @@
 kg</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr"/>
-      <c r="I14" s="19" t="inlineStr"/>
+      <c r="H14" s="17" t="inlineStr"/>
+      <c r="I14" s="17" t="inlineStr"/>
       <c r="J14" s="2" t="n"/>
-      <c r="K14" s="19" t="inlineStr"/>
-      <c r="L14" s="20" t="n"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
+      <c r="K14" s="17" t="inlineStr"/>
+      <c r="L14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>GE0002070
-アレック K-EML
-999 購入</t>
+          <t>GE0002070  999 購入
+アレック K-EML</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
@@ -1042,18 +1052,17 @@
 kg</t>
         </is>
       </c>
-      <c r="H15" s="19" t="inlineStr"/>
-      <c r="I15" s="19" t="inlineStr"/>
+      <c r="H15" s="17" t="inlineStr"/>
+      <c r="I15" s="17" t="inlineStr"/>
       <c r="J15" s="2" t="n"/>
-      <c r="K15" s="19" t="inlineStr"/>
-      <c r="L15" s="20" t="n"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
+      <c r="K15" s="17" t="inlineStr"/>
+      <c r="L15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>GE0003110
-ポエムＺＬ－３
-999 購入</t>
+          <t>GE0003110  999 購入
+ポエムZ L-3</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -1071,18 +1080,17 @@
 kg</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr"/>
-      <c r="I16" s="19" t="inlineStr"/>
+      <c r="H16" s="17" t="inlineStr"/>
+      <c r="I16" s="17" t="inlineStr"/>
       <c r="J16" s="2" t="n"/>
-      <c r="K16" s="19" t="inlineStr"/>
-      <c r="L16" s="20" t="n"/>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+      <c r="K16" s="17" t="inlineStr"/>
+      <c r="L16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>GE0006810
-バカダートミルクコーヒー SSH-181
-999 購入</t>
+          <t>GE0006810  999 購入
+バカダートミルクコーヒー SSH-181</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
@@ -1100,18 +1108,17 @@
 kg</t>
         </is>
       </c>
-      <c r="H17" s="19" t="inlineStr"/>
-      <c r="I17" s="19" t="inlineStr"/>
+      <c r="H17" s="17" t="inlineStr"/>
+      <c r="I17" s="17" t="inlineStr"/>
       <c r="J17" s="2" t="n"/>
-      <c r="K17" s="19" t="inlineStr"/>
-      <c r="L17" s="20" t="n"/>
-    </row>
-    <row r="18" ht="90" customHeight="1">
+      <c r="K17" s="17" t="inlineStr"/>
+      <c r="L17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>GE0004800
-コーヒーパウダーフレーバー YM-5309
-999 購入</t>
+          <t>GE0004800  999 購入
+コーヒーパウダーフレーバー YM-5309</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -1129,232 +1136,233 @@
 kg</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr"/>
-      <c r="I18" s="19" t="inlineStr"/>
+      <c r="H18" s="17" t="inlineStr"/>
+      <c r="I18" s="17" t="inlineStr"/>
       <c r="J18" s="2" t="n"/>
-      <c r="K18" s="19" t="inlineStr"/>
-      <c r="L18" s="20" t="n"/>
+      <c r="K18" s="17" t="inlineStr"/>
+      <c r="L18" s="19" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="21" t="n"/>
+      <c r="A19" s="20" t="n"/>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="22" t="n"/>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="21" t="n"/>
+      <c r="I19" s="21" t="n"/>
       <c r="J19" s="2" t="n"/>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="20" t="n"/>
+      <c r="K19" s="21" t="n"/>
+      <c r="L19" s="19" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="21" t="n"/>
+      <c r="A20" s="20" t="n"/>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="22" t="n"/>
-      <c r="I20" s="22" t="n"/>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="21" t="n"/>
       <c r="J20" s="2" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="20" t="n"/>
+      <c r="K20" s="21" t="n"/>
+      <c r="L20" s="19" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="21" t="n"/>
+      <c r="A21" s="20" t="n"/>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="22" t="n"/>
-      <c r="H21" s="22" t="n"/>
-      <c r="I21" s="22" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="21" t="n"/>
+      <c r="I21" s="21" t="n"/>
       <c r="J21" s="2" t="n"/>
-      <c r="K21" s="22" t="n"/>
-      <c r="L21" s="20" t="n"/>
+      <c r="K21" s="21" t="n"/>
+      <c r="L21" s="19" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="21" t="n"/>
+      <c r="A22" s="20" t="n"/>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
-      <c r="F22" s="22" t="n"/>
-      <c r="G22" s="22" t="n"/>
-      <c r="H22" s="22" t="n"/>
-      <c r="I22" s="22" t="n"/>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="21" t="n"/>
+      <c r="H22" s="21" t="n"/>
+      <c r="I22" s="21" t="n"/>
       <c r="J22" s="2" t="n"/>
-      <c r="K22" s="22" t="n"/>
-      <c r="L22" s="20" t="n"/>
+      <c r="K22" s="21" t="n"/>
+      <c r="L22" s="19" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="21" t="n"/>
+      <c r="A23" s="20" t="n"/>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
-      <c r="F23" s="22" t="n"/>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="22" t="n"/>
-      <c r="I23" s="22" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="21" t="n"/>
       <c r="J23" s="2" t="n"/>
-      <c r="K23" s="22" t="n"/>
-      <c r="L23" s="20" t="n"/>
+      <c r="K23" s="21" t="n"/>
+      <c r="L23" s="19" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="21" t="n"/>
+      <c r="A24" s="20" t="n"/>
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
-      <c r="F24" s="22" t="n"/>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="22" t="n"/>
-      <c r="I24" s="22" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="21" t="n"/>
       <c r="J24" s="2" t="n"/>
-      <c r="K24" s="22" t="n"/>
-      <c r="L24" s="20" t="n"/>
+      <c r="K24" s="21" t="n"/>
+      <c r="L24" s="19" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="21" t="n"/>
+      <c r="A25" s="20" t="n"/>
       <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
-      <c r="F25" s="22" t="n"/>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="22" t="n"/>
-      <c r="I25" s="22" t="n"/>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="21" t="n"/>
+      <c r="H25" s="21" t="n"/>
+      <c r="I25" s="21" t="n"/>
       <c r="J25" s="2" t="n"/>
-      <c r="K25" s="22" t="n"/>
-      <c r="L25" s="20" t="n"/>
+      <c r="K25" s="21" t="n"/>
+      <c r="L25" s="19" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="21" t="n"/>
+      <c r="A26" s="20" t="n"/>
       <c r="B26" s="2" t="n"/>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
-      <c r="F26" s="22" t="n"/>
-      <c r="G26" s="22" t="n"/>
-      <c r="H26" s="22" t="n"/>
-      <c r="I26" s="22" t="n"/>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="21" t="n"/>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="21" t="n"/>
       <c r="J26" s="2" t="n"/>
-      <c r="K26" s="22" t="n"/>
-      <c r="L26" s="20" t="n"/>
+      <c r="K26" s="21" t="n"/>
+      <c r="L26" s="19" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="21" t="n"/>
+      <c r="A27" s="20" t="n"/>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
-      <c r="F27" s="22" t="n"/>
-      <c r="G27" s="22" t="n"/>
-      <c r="H27" s="22" t="n"/>
-      <c r="I27" s="22" t="n"/>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="21" t="n"/>
+      <c r="H27" s="21" t="n"/>
+      <c r="I27" s="21" t="n"/>
       <c r="J27" s="2" t="n"/>
-      <c r="K27" s="22" t="n"/>
-      <c r="L27" s="20" t="n"/>
+      <c r="K27" s="21" t="n"/>
+      <c r="L27" s="19" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="21" t="n"/>
+      <c r="A28" s="20" t="n"/>
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
-      <c r="F28" s="22" t="n"/>
-      <c r="G28" s="22" t="n"/>
-      <c r="H28" s="22" t="n"/>
-      <c r="I28" s="22" t="n"/>
+      <c r="F28" s="21" t="n"/>
+      <c r="G28" s="21" t="n"/>
+      <c r="H28" s="21" t="n"/>
+      <c r="I28" s="21" t="n"/>
       <c r="J28" s="2" t="n"/>
-      <c r="K28" s="22" t="n"/>
-      <c r="L28" s="20" t="n"/>
+      <c r="K28" s="21" t="n"/>
+      <c r="L28" s="19" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="21" t="n"/>
+      <c r="A29" s="20" t="n"/>
       <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
-      <c r="F29" s="22" t="n"/>
-      <c r="G29" s="22" t="n"/>
-      <c r="H29" s="22" t="n"/>
-      <c r="I29" s="22" t="n"/>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="21" t="n"/>
+      <c r="H29" s="21" t="n"/>
+      <c r="I29" s="21" t="n"/>
       <c r="J29" s="2" t="n"/>
-      <c r="K29" s="22" t="n"/>
-      <c r="L29" s="20" t="n"/>
+      <c r="K29" s="21" t="n"/>
+      <c r="L29" s="19" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="21" t="n"/>
+      <c r="A30" s="20" t="n"/>
       <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
-      <c r="F30" s="22" t="n"/>
-      <c r="G30" s="22" t="n"/>
-      <c r="H30" s="22" t="n"/>
-      <c r="I30" s="22" t="n"/>
+      <c r="F30" s="21" t="n"/>
+      <c r="G30" s="21" t="n"/>
+      <c r="H30" s="21" t="n"/>
+      <c r="I30" s="21" t="n"/>
       <c r="J30" s="2" t="n"/>
-      <c r="K30" s="22" t="n"/>
-      <c r="L30" s="20" t="n"/>
+      <c r="K30" s="21" t="n"/>
+      <c r="L30" s="19" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="21" t="n"/>
+      <c r="A31" s="20" t="n"/>
       <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
-      <c r="F31" s="22" t="n"/>
-      <c r="G31" s="22" t="n"/>
-      <c r="H31" s="22" t="n"/>
-      <c r="I31" s="22" t="n"/>
+      <c r="F31" s="21" t="n"/>
+      <c r="G31" s="21" t="n"/>
+      <c r="H31" s="21" t="n"/>
+      <c r="I31" s="21" t="n"/>
       <c r="J31" s="2" t="n"/>
-      <c r="K31" s="22" t="n"/>
-      <c r="L31" s="20" t="n"/>
+      <c r="K31" s="21" t="n"/>
+      <c r="L31" s="19" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="21" t="n"/>
+      <c r="A32" s="20" t="n"/>
       <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
-      <c r="F32" s="22" t="n"/>
-      <c r="G32" s="22" t="n"/>
-      <c r="H32" s="22" t="n"/>
-      <c r="I32" s="22" t="n"/>
+      <c r="F32" s="21" t="n"/>
+      <c r="G32" s="21" t="n"/>
+      <c r="H32" s="21" t="n"/>
+      <c r="I32" s="21" t="n"/>
       <c r="J32" s="2" t="n"/>
-      <c r="K32" s="22" t="n"/>
-      <c r="L32" s="20" t="n"/>
-    </row>
-    <row r="33" ht="150" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="K32" s="21" t="n"/>
+      <c r="L32" s="19" t="n"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="B33" s="24" t="n"/>
-      <c r="C33" s="24" t="n"/>
-      <c r="D33" s="24" t="n"/>
-      <c r="E33" s="24" t="n"/>
-      <c r="F33" s="24" t="n"/>
-      <c r="G33" s="24" t="n"/>
-      <c r="H33" s="24" t="n"/>
-      <c r="I33" s="24" t="n"/>
-      <c r="J33" s="24" t="n"/>
-      <c r="K33" s="24" t="n"/>
-      <c r="L33" s="25" t="n"/>
+      <c r="B33" s="23" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="23" t="n"/>
+      <c r="F33" s="23" t="n"/>
+      <c r="G33" s="23" t="n"/>
+      <c r="H33" s="23" t="n"/>
+      <c r="I33" s="23" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="23" t="n"/>
+      <c r="L33" s="24" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="99">
+  <mergeCells count="101">
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="K24:L24"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="C5:G5"/>
+    <mergeCell ref="H2:J2"/>
     <mergeCell ref="I26:J26"/>
     <mergeCell ref="K26:L26"/>
     <mergeCell ref="A7:B7"/>
@@ -1365,6 +1373,7 @@
     <mergeCell ref="I9:J10"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A26:E26"/>
+    <mergeCell ref="K2:L2"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="I20:J20"/>
@@ -1399,20 +1408,19 @@
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="K25:L25"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="G2:H2"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="C2:E2"/>
     <mergeCell ref="K29:L29"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="K31:L31"/>
-    <mergeCell ref="I2:L2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A9:E10"/>
     <mergeCell ref="I21:J21"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="K8:L8"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="K23:L23"/>
@@ -1424,6 +1432,7 @@
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A8:J8"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="I27:J27"/>
@@ -1432,7 +1441,6 @@
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A8:L8"/>
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I28:J28"/>
     <mergeCell ref="K22:L22"/>
@@ -1441,6 +1449,7 @@
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="K12:L12"/>
+    <mergeCell ref="C2:D2"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="K14:L14"/>

--- a/output/IMG_9688.xlsx
+++ b/output/IMG_9688.xlsx
@@ -902,7 +902,7 @@
       <c r="C6" s="13" t="n"/>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>ドライ・マッシュ ポテト(ふ・ポ風味)造粒品</t>
+          <t>ドライ・マッシュ ポテト(ふ・ぱい風味)造粒品</t>
         </is>
       </c>
       <c r="E6" s="12" t="n"/>
@@ -1123,7 +1123,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>GE0006280        999 購入
+          <t>GB0006280        999 購入
 Shayco 『80-ポテューズ2ポテ』</t>
         </is>
       </c>
@@ -1162,7 +1162,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>GE0005150        999 購入
+          <t>GB0005150        999 購入
 IATA INSTANT COFFEE FR-2132(微粉り)</t>
         </is>
       </c>
@@ -1201,7 +1201,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>GE0004220        999 購入
+          <t>GB0004220        999 購入
 鎌塚レシダー</t>
         </is>
       </c>
@@ -1240,7 +1240,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>GE0003040        999 購入
+          <t>GB0003040        999 購入
 ステラス×200(大茂植食)</t>
         </is>
       </c>
@@ -1279,7 +1279,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>GE0002070        999 購入
+          <t>GB0002070        999 購入
 フッジ K-EM.</t>
         </is>
       </c>
@@ -1318,7 +1318,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>GE0003110        999 購入
+          <t>GB0003110        999 購入
 ボエムZ 1-3</t>
         </is>
       </c>
@@ -1357,8 +1357,8 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>GE0006810        999 購入
-ハダーー『ミナーズ SSH-181</t>
+          <t>GB0006810        999 購入
+ハダーー『 ミナチュー SSH-181</t>
         </is>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -1396,8 +1396,8 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>GE0004800        999 購入
-コーヒー ダターブレーデー YM-5309</t>
+          <t>GB0004800        999 購入
+コーヒー ダダーブレーダー YM-5309</t>
         </is>
       </c>
       <c r="B19" s="12" t="n"/>

--- a/output/IMG_9688.xlsx
+++ b/output/IMG_9688.xlsx
@@ -902,7 +902,7 @@
       <c r="C6" s="13" t="n"/>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>ドライ・マッシュ ポテト(ふ・ぱい風味)造粒品</t>
+          <t>ドライ・マッシュ ポテト(ふ・ポ風味)造粒品</t>
         </is>
       </c>
       <c r="E6" s="12" t="n"/>
@@ -1123,7 +1123,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>GB0006280        999 購入
+          <t>GE0006280        999 購入
 Shayco 『80-ポテューズ2ポテ』</t>
         </is>
       </c>
@@ -1162,7 +1162,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>GB0005150        999 購入
+          <t>GE0005150        999 購入
 IATA INSTANT COFFEE FR-2132(微粉り)</t>
         </is>
       </c>
@@ -1201,7 +1201,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>GB0004220        999 購入
+          <t>GE0004220        999 購入
 鎌塚レシダー</t>
         </is>
       </c>
@@ -1240,7 +1240,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>GB0003040        999 購入
+          <t>GE0003040        999 購入
 ステラス×200(大茂植食)</t>
         </is>
       </c>
@@ -1279,7 +1279,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>GB0002070        999 購入
+          <t>GE0002070        999 購入
 フッジ K-EM.</t>
         </is>
       </c>
@@ -1318,7 +1318,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>GB0003110        999 購入
+          <t>GE0003110        999 購入
 ボエムZ 1-3</t>
         </is>
       </c>
@@ -1357,8 +1357,8 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>GB0006810        999 購入
-ハダーー『 ミナチュー SSH-181</t>
+          <t>GE0006810        999 購入
+ハダーー『シモーズ SSH-181</t>
         </is>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -1396,8 +1396,8 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>GB0004800        999 購入
-コーヒー ダダーブレーダー YM-5309</t>
+          <t>GE0004800        999 購入
+コーヒー ダターフレーバー YM-5309</t>
         </is>
       </c>
       <c r="B19" s="12" t="n"/>

--- a/output/IMG_9688.xlsx
+++ b/output/IMG_9688.xlsx
@@ -1202,7 +1202,7 @@
       <c r="A14" s="29" t="inlineStr">
         <is>
           <t>GE0004220        999 購入
-鎌塚レシダー</t>
+鎌塚レシピダー</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -1241,7 +1241,7 @@
       <c r="A15" s="29" t="inlineStr">
         <is>
           <t>GE0003040        999 購入
-ステラス×200(大茂植食)</t>
+ステラス×200(大宮機食)</t>
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
@@ -1358,7 +1358,7 @@
       <c r="A18" s="29" t="inlineStr">
         <is>
           <t>GE0006810        999 購入
-ハダーー『シモーズ SSH-181</t>
+ハダーロー ミナーズ SSH-181</t>
         </is>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -1695,7 +1695,7 @@
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="30" t="inlineStr">
         <is>
-          <t>調合票</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="B30" s="31" t="n"/>

--- a/output/IMG_9688.xlsx
+++ b/output/IMG_9688.xlsx
@@ -742,7 +742,7 @@
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>0000056481</t>
+          <t>0000056481 1</t>
         </is>
       </c>
       <c r="E2" s="5" t="n"/>
@@ -757,7 +757,7 @@
       <c r="J2" s="6" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2018/12/06</t>
+          <t>2018/12/05</t>
         </is>
       </c>
       <c r="L2" s="5" t="n"/>
@@ -810,7 +810,7 @@
       <c r="C4" s="10" t="n"/>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>S00000200 製造1課 倉庫</t>
+          <t>S00000200 製造１課 倉庫</t>
         </is>
       </c>
       <c r="E4" s="9" t="n"/>
@@ -902,7 +902,7 @@
       <c r="C6" s="13" t="n"/>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>ドライ・マッシュ ポテト(ふ・ポ風味)造粒品</t>
+          <t>クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
         </is>
       </c>
       <c r="E6" s="12" t="n"/>
@@ -966,7 +966,7 @@
       <c r="Q7" s="13" t="n"/>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>S00000200 製造1課 倉庫</t>
+          <t>S00000200 製造１課 倉庫</t>
         </is>
       </c>
       <c r="S7" s="12" t="n"/>
@@ -984,11 +984,7 @@
       </c>
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="n"/>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>0000056481</t>
-        </is>
-      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="12" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
@@ -1123,8 +1119,8 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>GE0006280        999 購入
-Shayco 『80-ポテューズ2ポテ』</t>
+          <t>GE0006280
+Wheyco W80-パフォーマンスアカデミー</t>
         </is>
       </c>
       <c r="B12" s="26" t="n"/>
@@ -1139,17 +1135,22 @@
       <c r="K12" s="27" t="n"/>
       <c r="L12" s="28" t="inlineStr">
         <is>
-          <t>89.8383</t>
+          <t>999 購入</t>
         </is>
       </c>
       <c r="M12" s="27" t="n"/>
       <c r="N12" s="28" t="inlineStr">
         <is>
-          <t>360.00 kg</t>
+          <t>89.8383</t>
         </is>
       </c>
       <c r="O12" s="27" t="n"/>
-      <c r="P12" s="28" t="n"/>
+      <c r="P12" s="28" t="inlineStr">
+        <is>
+          <t>360.00
+kg</t>
+        </is>
+      </c>
       <c r="Q12" s="27" t="n"/>
       <c r="R12" s="28" t="n"/>
       <c r="S12" s="26" t="n"/>
@@ -1162,8 +1163,8 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>GE0005150        999 購入
-IATA INSTANT COFFEE FR-2132(微粉り)</t>
+          <t>GE0005150
+TATA INSTANT COFFEE FR-2132（深煎り）</t>
         </is>
       </c>
       <c r="B13" s="12" t="n"/>
@@ -1178,17 +1179,22 @@
       <c r="K13" s="13" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>5.9893</t>
+          <t>999 購入</t>
         </is>
       </c>
       <c r="M13" s="13" t="n"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>24.00 kg</t>
+          <t>5.9893</t>
         </is>
       </c>
       <c r="O13" s="13" t="n"/>
-      <c r="P13" s="11" t="n"/>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>24.00
+kg</t>
+        </is>
+      </c>
       <c r="Q13" s="13" t="n"/>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="12" t="n"/>
@@ -1201,8 +1207,8 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>GE0004220        999 購入
-鎌塚レシピダー</t>
+          <t>GE0004220
+練乳パウダー</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -1217,17 +1223,22 @@
       <c r="K14" s="13" t="n"/>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>2.2959</t>
+          <t>999 購入</t>
         </is>
       </c>
       <c r="M14" s="13" t="n"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>9.20 kg</t>
+          <t>2.2959</t>
         </is>
       </c>
       <c r="O14" s="13" t="n"/>
-      <c r="P14" s="11" t="n"/>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>9.20
+kg</t>
+        </is>
+      </c>
       <c r="Q14" s="13" t="n"/>
       <c r="R14" s="11" t="n"/>
       <c r="S14" s="12" t="n"/>
@@ -1240,8 +1251,8 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>GE0003040        999 購入
-ステラス×200(大宮機食)</t>
+          <t>GE0003040
+ステラロース200（大宮糧食）</t>
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
@@ -1256,17 +1267,22 @@
       <c r="K15" s="13" t="n"/>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>0.2795</t>
+          <t>999 購入</t>
         </is>
       </c>
       <c r="M15" s="13" t="n"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>1.12 kg</t>
+          <t>0.2795</t>
         </is>
       </c>
       <c r="O15" s="13" t="n"/>
-      <c r="P15" s="11" t="n"/>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>1.12
+kg</t>
+        </is>
+      </c>
       <c r="Q15" s="13" t="n"/>
       <c r="R15" s="11" t="n"/>
       <c r="S15" s="12" t="n"/>
@@ -1279,8 +1295,8 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>GE0002070        999 購入
-フッジ K-EM.</t>
+          <t>GE0002070
+ソレック K-EML</t>
         </is>
       </c>
       <c r="B16" s="12" t="n"/>
@@ -1295,17 +1311,22 @@
       <c r="K16" s="13" t="n"/>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>0.2995</t>
+          <t>999 購入</t>
         </is>
       </c>
       <c r="M16" s="13" t="n"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>1.20 kg</t>
+          <t>0.2995</t>
         </is>
       </c>
       <c r="O16" s="13" t="n"/>
-      <c r="P16" s="11" t="n"/>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>1.20
+kg</t>
+        </is>
+      </c>
       <c r="Q16" s="13" t="n"/>
       <c r="R16" s="11" t="n"/>
       <c r="S16" s="12" t="n"/>
@@ -1318,8 +1339,8 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>GE0003110        999 購入
-ボエムZ 1-3</t>
+          <t>GE0003110
+ポエムＺＬ－３</t>
         </is>
       </c>
       <c r="B17" s="12" t="n"/>
@@ -1334,17 +1355,22 @@
       <c r="K17" s="13" t="n"/>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>0.4991</t>
+          <t>999 購入</t>
         </is>
       </c>
       <c r="M17" s="13" t="n"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>2.00 kg</t>
+          <t>0.4991</t>
         </is>
       </c>
       <c r="O17" s="13" t="n"/>
-      <c r="P17" s="11" t="n"/>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>2.00
+kg</t>
+        </is>
+      </c>
       <c r="Q17" s="13" t="n"/>
       <c r="R17" s="11" t="n"/>
       <c r="S17" s="12" t="n"/>
@@ -1357,8 +1383,8 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>GE0006810        999 購入
-ハダーロー ミナーズ SSH-181</t>
+          <t>GE0006810
+バクダードミルクコーヒー SSH-181</t>
         </is>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -1373,17 +1399,22 @@
       <c r="K18" s="13" t="n"/>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>0.4991</t>
+          <t>999 購入</t>
         </is>
       </c>
       <c r="M18" s="13" t="n"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>2.00 kg</t>
+          <t>0.4991</t>
         </is>
       </c>
       <c r="O18" s="13" t="n"/>
-      <c r="P18" s="11" t="n"/>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>2.00
+kg</t>
+        </is>
+      </c>
       <c r="Q18" s="13" t="n"/>
       <c r="R18" s="11" t="n"/>
       <c r="S18" s="12" t="n"/>
@@ -1396,8 +1427,8 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>GE0004800        999 購入
-コーヒー ダターフレーバー YM-5309</t>
+          <t>GE0004800
+コーヒーパウダーフレーバー YM-5309</t>
         </is>
       </c>
       <c r="B19" s="12" t="n"/>
@@ -1412,17 +1443,22 @@
       <c r="K19" s="13" t="n"/>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>0.2995</t>
+          <t>999 購入</t>
         </is>
       </c>
       <c r="M19" s="13" t="n"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>1.20 kg</t>
+          <t>0.2995</t>
         </is>
       </c>
       <c r="O19" s="13" t="n"/>
-      <c r="P19" s="11" t="n"/>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>1.20
+kg</t>
+        </is>
+      </c>
       <c r="Q19" s="13" t="n"/>
       <c r="R19" s="11" t="n"/>
       <c r="S19" s="12" t="n"/>

--- a/output/IMG_9688.xlsx
+++ b/output/IMG_9688.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="製造指図書" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,16 +27,20 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="12"/>
     </font>
     <font>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="00000000"/>
       <sz val="22"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -742,7 +746,7 @@
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>0000056481 1</t>
+          <t>0000056481　1</t>
         </is>
       </c>
       <c r="E2" s="5" t="n"/>
@@ -810,7 +814,7 @@
       <c r="C4" s="10" t="n"/>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>S00000200 製造１課 倉庫</t>
+          <t>S00000200 製造１課　倉庫</t>
         </is>
       </c>
       <c r="E4" s="9" t="n"/>
@@ -944,7 +948,7 @@
       <c r="C7" s="13" t="n"/>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>20 仕込</t>
+          <t>20　仕込</t>
         </is>
       </c>
       <c r="E7" s="12" t="n"/>
@@ -966,7 +970,7 @@
       <c r="Q7" s="13" t="n"/>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>S00000200 製造１課 倉庫</t>
+          <t>S00000200 製造１課　倉庫</t>
         </is>
       </c>
       <c r="S7" s="12" t="n"/>
@@ -1119,7 +1123,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>GE0006280
+          <t>GE0006280        999 購入
 Wheyco W80-パフォーマンスアカデミー</t>
         </is>
       </c>
@@ -1135,22 +1139,18 @@
       <c r="K12" s="27" t="n"/>
       <c r="L12" s="28" t="inlineStr">
         <is>
-          <t>999 購入</t>
+          <t>89.8383</t>
         </is>
       </c>
       <c r="M12" s="27" t="n"/>
       <c r="N12" s="28" t="inlineStr">
         <is>
-          <t>89.8383</t>
-        </is>
-      </c>
-      <c r="O12" s="27" t="n"/>
-      <c r="P12" s="28" t="inlineStr">
-        <is>
           <t>360.00
 kg</t>
         </is>
       </c>
+      <c r="O12" s="27" t="n"/>
+      <c r="P12" s="28" t="n"/>
       <c r="Q12" s="27" t="n"/>
       <c r="R12" s="28" t="n"/>
       <c r="S12" s="26" t="n"/>
@@ -1163,7 +1163,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>GE0005150
+          <t>GE0005150        999 購入
 TATA INSTANT COFFEE FR-2132（深煎り）</t>
         </is>
       </c>
@@ -1179,22 +1179,18 @@
       <c r="K13" s="13" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>999 購入</t>
+          <t>5.9893</t>
         </is>
       </c>
       <c r="M13" s="13" t="n"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>5.9893</t>
-        </is>
-      </c>
-      <c r="O13" s="13" t="n"/>
-      <c r="P13" s="11" t="inlineStr">
-        <is>
           <t>24.00
 kg</t>
         </is>
       </c>
+      <c r="O13" s="13" t="n"/>
+      <c r="P13" s="11" t="n"/>
       <c r="Q13" s="13" t="n"/>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="12" t="n"/>
@@ -1207,7 +1203,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>GE0004220
+          <t>GE0004220        999 購入
 練乳パウダー</t>
         </is>
       </c>
@@ -1223,22 +1219,18 @@
       <c r="K14" s="13" t="n"/>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>999 購入</t>
+          <t>2.2959</t>
         </is>
       </c>
       <c r="M14" s="13" t="n"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>2.2959</t>
-        </is>
-      </c>
-      <c r="O14" s="13" t="n"/>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
           <t>9.20
 kg</t>
         </is>
       </c>
+      <c r="O14" s="13" t="n"/>
+      <c r="P14" s="11" t="n"/>
       <c r="Q14" s="13" t="n"/>
       <c r="R14" s="11" t="n"/>
       <c r="S14" s="12" t="n"/>
@@ -1251,7 +1243,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>GE0003040
+          <t>GE0003040        999 購入
 ステラロース200（大宮糧食）</t>
         </is>
       </c>
@@ -1267,22 +1259,18 @@
       <c r="K15" s="13" t="n"/>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>999 購入</t>
+          <t>0.2795</t>
         </is>
       </c>
       <c r="M15" s="13" t="n"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>0.2795</t>
-        </is>
-      </c>
-      <c r="O15" s="13" t="n"/>
-      <c r="P15" s="11" t="inlineStr">
-        <is>
           <t>1.12
 kg</t>
         </is>
       </c>
+      <c r="O15" s="13" t="n"/>
+      <c r="P15" s="11" t="n"/>
       <c r="Q15" s="13" t="n"/>
       <c r="R15" s="11" t="n"/>
       <c r="S15" s="12" t="n"/>
@@ -1295,7 +1283,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>GE0002070
+          <t>GE0002070        999 購入
 ソレック K-EML</t>
         </is>
       </c>
@@ -1311,22 +1299,18 @@
       <c r="K16" s="13" t="n"/>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>999 購入</t>
+          <t>0.2995</t>
         </is>
       </c>
       <c r="M16" s="13" t="n"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>0.2995</t>
-        </is>
-      </c>
-      <c r="O16" s="13" t="n"/>
-      <c r="P16" s="11" t="inlineStr">
-        <is>
           <t>1.20
 kg</t>
         </is>
       </c>
+      <c r="O16" s="13" t="n"/>
+      <c r="P16" s="11" t="n"/>
       <c r="Q16" s="13" t="n"/>
       <c r="R16" s="11" t="n"/>
       <c r="S16" s="12" t="n"/>
@@ -1339,7 +1323,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>GE0003110
+          <t>GE0003110        999 購入
 ポエムＺＬ－３</t>
         </is>
       </c>
@@ -1355,22 +1339,18 @@
       <c r="K17" s="13" t="n"/>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>999 購入</t>
+          <t>0.4991</t>
         </is>
       </c>
       <c r="M17" s="13" t="n"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>0.4991</t>
-        </is>
-      </c>
-      <c r="O17" s="13" t="n"/>
-      <c r="P17" s="11" t="inlineStr">
-        <is>
           <t>2.00
 kg</t>
         </is>
       </c>
+      <c r="O17" s="13" t="n"/>
+      <c r="P17" s="11" t="n"/>
       <c r="Q17" s="13" t="n"/>
       <c r="R17" s="11" t="n"/>
       <c r="S17" s="12" t="n"/>
@@ -1383,7 +1363,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>GE0006810
+          <t>GE0006810        999 購入
 バクダードミルクコーヒー SSH-181</t>
         </is>
       </c>
@@ -1399,22 +1379,18 @@
       <c r="K18" s="13" t="n"/>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>999 購入</t>
+          <t>0.4991</t>
         </is>
       </c>
       <c r="M18" s="13" t="n"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>0.4991</t>
-        </is>
-      </c>
-      <c r="O18" s="13" t="n"/>
-      <c r="P18" s="11" t="inlineStr">
-        <is>
           <t>2.00
 kg</t>
         </is>
       </c>
+      <c r="O18" s="13" t="n"/>
+      <c r="P18" s="11" t="n"/>
       <c r="Q18" s="13" t="n"/>
       <c r="R18" s="11" t="n"/>
       <c r="S18" s="12" t="n"/>
@@ -1427,7 +1403,7 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>GE0004800
+          <t>GE0004800        999 購入
 コーヒーパウダーフレーバー YM-5309</t>
         </is>
       </c>
@@ -1443,22 +1419,18 @@
       <c r="K19" s="13" t="n"/>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>999 購入</t>
+          <t>0.2995</t>
         </is>
       </c>
       <c r="M19" s="13" t="n"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>0.2995</t>
-        </is>
-      </c>
-      <c r="O19" s="13" t="n"/>
-      <c r="P19" s="11" t="inlineStr">
-        <is>
           <t>1.20
 kg</t>
         </is>
       </c>
+      <c r="O19" s="13" t="n"/>
+      <c r="P19" s="11" t="n"/>
       <c r="Q19" s="13" t="n"/>
       <c r="R19" s="11" t="n"/>
       <c r="S19" s="12" t="n"/>

--- a/output/IMG_9688.xlsx
+++ b/output/IMG_9688.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +233,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -677,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X30"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.7265625" customWidth="1" min="1" max="1"/>
@@ -746,29 +749,33 @@
       <c r="C2" s="6" t="n"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>0000056481　1</t>
+          <t>0000056481</t>
         </is>
       </c>
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
       </c>
-      <c r="J2" s="6" t="n"/>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>2018/12/05</t>
         </is>
       </c>
-      <c r="L2" s="5" t="n"/>
       <c r="M2" s="5" t="n"/>
-      <c r="N2" s="6" t="n"/>
-      <c r="O2" s="4" t="n"/>
-      <c r="P2" s="5" t="n"/>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="4" t="n"/>
       <c r="Q2" s="5" t="n"/>
       <c r="R2" s="5" t="n"/>
       <c r="S2" s="5" t="n"/>
@@ -779,959 +786,1011 @@
       <c r="X2" s="6" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
-      <c r="I3" s="7" t="n"/>
-      <c r="J3" s="7" t="n"/>
-      <c r="K3" s="7" t="n"/>
-      <c r="L3" s="7" t="n"/>
-      <c r="M3" s="7" t="n"/>
-      <c r="N3" s="7" t="n"/>
-      <c r="O3" s="7" t="n"/>
-      <c r="P3" s="7" t="n"/>
-      <c r="Q3" s="7" t="n"/>
-      <c r="R3" s="7" t="n"/>
-      <c r="S3" s="7" t="n"/>
-      <c r="T3" s="7" t="n"/>
-      <c r="U3" s="7" t="n"/>
-      <c r="V3" s="7" t="n"/>
-      <c r="W3" s="7" t="n"/>
-      <c r="X3" s="7" t="n"/>
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="8" t="n"/>
+      <c r="Q3" s="8" t="n"/>
+      <c r="R3" s="8" t="n"/>
+      <c r="S3" s="8" t="n"/>
+      <c r="T3" s="8" t="n"/>
+      <c r="U3" s="8" t="n"/>
+      <c r="V3" s="8" t="n"/>
+      <c r="W3" s="8" t="n"/>
+      <c r="X3" s="8" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>手配先</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>S00000200 製造１課　倉庫</t>
         </is>
       </c>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="9" t="n"/>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
-      <c r="M4" s="9" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t>手配調整期</t>
         </is>
       </c>
-      <c r="P4" s="9" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="9" t="inlineStr">
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="10" t="inlineStr">
         <is>
           <t>2018/12/14</t>
         </is>
       </c>
-      <c r="S4" s="9" t="n"/>
-      <c r="T4" s="9" t="n"/>
-      <c r="U4" s="9" t="n"/>
-      <c r="V4" s="9" t="n"/>
-      <c r="W4" s="9" t="n"/>
-      <c r="X4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="11" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>品目CD</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>HA0002610</t>
         </is>
       </c>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>工順</t>
         </is>
       </c>
-      <c r="L5" s="13" t="n"/>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="13" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>発注手配数</t>
         </is>
       </c>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="12" t="inlineStr">
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="13" t="inlineStr">
         <is>
           <t>400.72 kg</t>
         </is>
       </c>
-      <c r="S5" s="12" t="n"/>
-      <c r="T5" s="12" t="n"/>
-      <c r="U5" s="12" t="n"/>
-      <c r="V5" s="12" t="n"/>
-      <c r="W5" s="12" t="n"/>
-      <c r="X5" s="13" t="n"/>
+      <c r="S5" s="13" t="n"/>
+      <c r="T5" s="13" t="n"/>
+      <c r="U5" s="13" t="n"/>
+      <c r="V5" s="13" t="n"/>
+      <c r="W5" s="13" t="n"/>
+      <c r="X5" s="14" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>品目名</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="13" t="n"/>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>製番</t>
         </is>
       </c>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="13" t="n"/>
-      <c r="R6" s="12" t="inlineStr">
+      <c r="P6" s="13" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="13" t="inlineStr">
         <is>
           <t>0000051090</t>
         </is>
       </c>
-      <c r="S6" s="12" t="n"/>
-      <c r="T6" s="12" t="n"/>
-      <c r="U6" s="12" t="n"/>
-      <c r="V6" s="12" t="n"/>
-      <c r="W6" s="12" t="n"/>
-      <c r="X6" s="13" t="n"/>
+      <c r="S6" s="13" t="n"/>
+      <c r="T6" s="13" t="n"/>
+      <c r="U6" s="13" t="n"/>
+      <c r="V6" s="13" t="n"/>
+      <c r="W6" s="13" t="n"/>
+      <c r="X6" s="14" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>手配内容</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>20　仕込</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="13" t="n"/>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13" t="n"/>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="14" t="n"/>
+      <c r="O7" s="12" t="inlineStr">
         <is>
           <t>完成入庫</t>
         </is>
       </c>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="13" t="n"/>
-      <c r="R7" s="12" t="inlineStr">
+      <c r="P7" s="13" t="n"/>
+      <c r="Q7" s="14" t="n"/>
+      <c r="R7" s="13" t="inlineStr">
         <is>
           <t>S00000200 製造１課　倉庫</t>
         </is>
       </c>
-      <c r="S7" s="12" t="n"/>
-      <c r="T7" s="12" t="n"/>
-      <c r="U7" s="12" t="n"/>
-      <c r="V7" s="12" t="n"/>
-      <c r="W7" s="12" t="n"/>
-      <c r="X7" s="13" t="n"/>
+      <c r="S7" s="13" t="n"/>
+      <c r="T7" s="13" t="n"/>
+      <c r="U7" s="13" t="n"/>
+      <c r="V7" s="13" t="n"/>
+      <c r="W7" s="13" t="n"/>
+      <c r="X7" s="14" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>ロットNo.</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="13" t="n"/>
+      <c r="J8" s="13" t="n"/>
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="14" t="n"/>
+      <c r="O8" s="12" t="inlineStr">
         <is>
           <t>完成日</t>
         </is>
       </c>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="12" t="n"/>
-      <c r="S8" s="12" t="n"/>
-      <c r="T8" s="12" t="n"/>
-      <c r="U8" s="12" t="n"/>
-      <c r="V8" s="12" t="n"/>
-      <c r="W8" s="12" t="n"/>
-      <c r="X8" s="13" t="n"/>
+      <c r="P8" s="13" t="n"/>
+      <c r="Q8" s="14" t="n"/>
+      <c r="R8" s="13" t="n"/>
+      <c r="S8" s="13" t="n"/>
+      <c r="T8" s="13" t="n"/>
+      <c r="U8" s="13" t="n"/>
+      <c r="V8" s="13" t="n"/>
+      <c r="W8" s="13" t="n"/>
+      <c r="X8" s="14" t="n"/>
     </row>
     <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>調合票</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
-      <c r="J9" s="14" t="n"/>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="14" t="n"/>
-      <c r="N9" s="14" t="n"/>
-      <c r="O9" s="14" t="n"/>
-      <c r="P9" s="14" t="n"/>
-      <c r="Q9" s="14" t="n"/>
-      <c r="R9" s="14" t="n"/>
-      <c r="S9" s="14" t="n"/>
-      <c r="T9" s="14" t="n"/>
-      <c r="U9" s="14" t="n"/>
-      <c r="V9" s="14" t="n"/>
-      <c r="W9" s="14" t="n"/>
-      <c r="X9" s="14" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
+      <c r="K9" s="15" t="n"/>
+      <c r="L9" s="15" t="n"/>
+      <c r="M9" s="15" t="n"/>
+      <c r="N9" s="15" t="n"/>
+      <c r="O9" s="15" t="n"/>
+      <c r="P9" s="15" t="n"/>
+      <c r="Q9" s="15" t="n"/>
+      <c r="R9" s="15" t="n"/>
+      <c r="S9" s="15" t="n"/>
+      <c r="T9" s="15" t="n"/>
+      <c r="U9" s="15" t="n"/>
+      <c r="V9" s="15" t="n"/>
+      <c r="W9" s="15" t="n"/>
+      <c r="X9" s="15" t="n"/>
     </row>
     <row r="10" ht="14.5" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>成分名</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="n"/>
-      <c r="K10" s="17" t="n"/>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="18" t="n"/>
+      <c r="L10" s="19" t="inlineStr">
         <is>
           <t>原単位</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n"/>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="M10" s="18" t="n"/>
+      <c r="N10" s="19" t="inlineStr">
         <is>
           <t>分量</t>
         </is>
       </c>
-      <c r="O10" s="17" t="n"/>
-      <c r="P10" s="18" t="inlineStr">
+      <c r="O10" s="18" t="n"/>
+      <c r="P10" s="19" t="inlineStr">
         <is>
           <t>検量者</t>
         </is>
       </c>
-      <c r="Q10" s="17" t="n"/>
-      <c r="R10" s="18" t="inlineStr">
+      <c r="Q10" s="18" t="n"/>
+      <c r="R10" s="19" t="inlineStr">
         <is>
           <t>原料ロット</t>
         </is>
       </c>
-      <c r="S10" s="16" t="n"/>
-      <c r="T10" s="16" t="n"/>
-      <c r="U10" s="16" t="n"/>
-      <c r="V10" s="17" t="n"/>
-      <c r="W10" s="16" t="inlineStr">
+      <c r="S10" s="17" t="n"/>
+      <c r="T10" s="17" t="n"/>
+      <c r="U10" s="17" t="n"/>
+      <c r="V10" s="18" t="n"/>
+      <c r="W10" s="17" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="X10" s="17" t="n"/>
+      <c r="X10" s="18" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="19" t="n"/>
-      <c r="B11" s="20" t="n"/>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="22" t="n"/>
-      <c r="M11" s="23" t="n"/>
-      <c r="N11" s="22" t="n"/>
-      <c r="O11" s="23" t="n"/>
-      <c r="P11" s="22" t="n"/>
-      <c r="Q11" s="23" t="n"/>
-      <c r="R11" s="24" t="n"/>
-      <c r="S11" s="20" t="n"/>
-      <c r="T11" s="20" t="n"/>
-      <c r="U11" s="20" t="n"/>
-      <c r="V11" s="21" t="n"/>
-      <c r="W11" s="20" t="n"/>
-      <c r="X11" s="21" t="n"/>
+      <c r="A11" s="20" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="21" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="22" t="n"/>
+      <c r="L11" s="23" t="n"/>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="23" t="n"/>
+      <c r="O11" s="24" t="n"/>
+      <c r="P11" s="23" t="n"/>
+      <c r="Q11" s="24" t="n"/>
+      <c r="R11" s="25" t="n"/>
+      <c r="S11" s="21" t="n"/>
+      <c r="T11" s="21" t="n"/>
+      <c r="U11" s="21" t="n"/>
+      <c r="V11" s="22" t="n"/>
+      <c r="W11" s="21" t="n"/>
+      <c r="X11" s="22" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>GE0006280        999 購入
 Wheyco W80-パフォーマンスアカデミー</t>
         </is>
       </c>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="27" t="n"/>
-      <c r="L12" s="28" t="inlineStr">
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="27" t="n"/>
+      <c r="H12" s="27" t="n"/>
+      <c r="I12" s="27" t="n"/>
+      <c r="J12" s="27" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="29" t="inlineStr">
         <is>
           <t>89.8383</t>
         </is>
       </c>
-      <c r="M12" s="27" t="n"/>
-      <c r="N12" s="28" t="inlineStr">
+      <c r="M12" s="28" t="n"/>
+      <c r="N12" s="29" t="inlineStr">
         <is>
           <t>360.00
 kg</t>
         </is>
       </c>
-      <c r="O12" s="27" t="n"/>
-      <c r="P12" s="28" t="n"/>
-      <c r="Q12" s="27" t="n"/>
-      <c r="R12" s="28" t="n"/>
-      <c r="S12" s="26" t="n"/>
-      <c r="T12" s="26" t="n"/>
-      <c r="U12" s="26" t="n"/>
-      <c r="V12" s="27" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="27" t="n"/>
+      <c r="O12" s="28" t="n"/>
+      <c r="P12" s="29" t="n"/>
+      <c r="Q12" s="28" t="n"/>
+      <c r="R12" s="29" t="n"/>
+      <c r="S12" s="27" t="n"/>
+      <c r="T12" s="27" t="n"/>
+      <c r="U12" s="27" t="n"/>
+      <c r="V12" s="28" t="n"/>
+      <c r="W12" s="27" t="n"/>
+      <c r="X12" s="28" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>GE0005150        999 購入
 TATA INSTANT COFFEE FR-2132（深煎り）</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="13" t="n"/>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
+      <c r="J13" s="13" t="n"/>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>5.9893</t>
         </is>
       </c>
-      <c r="M13" s="13" t="n"/>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="M13" s="14" t="n"/>
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t>24.00
 kg</t>
         </is>
       </c>
-      <c r="O13" s="13" t="n"/>
-      <c r="P13" s="11" t="n"/>
-      <c r="Q13" s="13" t="n"/>
-      <c r="R13" s="11" t="n"/>
-      <c r="S13" s="12" t="n"/>
-      <c r="T13" s="12" t="n"/>
-      <c r="U13" s="12" t="n"/>
-      <c r="V13" s="13" t="n"/>
-      <c r="W13" s="12" t="n"/>
-      <c r="X13" s="13" t="n"/>
+      <c r="O13" s="14" t="n"/>
+      <c r="P13" s="12" t="n"/>
+      <c r="Q13" s="14" t="n"/>
+      <c r="R13" s="12" t="n"/>
+      <c r="S13" s="13" t="n"/>
+      <c r="T13" s="13" t="n"/>
+      <c r="U13" s="13" t="n"/>
+      <c r="V13" s="14" t="n"/>
+      <c r="W13" s="13" t="n"/>
+      <c r="X13" s="14" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>GE0004220        999 購入
 練乳パウダー</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="13" t="n"/>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="13" t="n"/>
+      <c r="J14" s="13" t="n"/>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>2.2959</t>
         </is>
       </c>
-      <c r="M14" s="13" t="n"/>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="M14" s="14" t="n"/>
+      <c r="N14" s="12" t="inlineStr">
         <is>
           <t>9.20
 kg</t>
         </is>
       </c>
-      <c r="O14" s="13" t="n"/>
-      <c r="P14" s="11" t="n"/>
-      <c r="Q14" s="13" t="n"/>
-      <c r="R14" s="11" t="n"/>
-      <c r="S14" s="12" t="n"/>
-      <c r="T14" s="12" t="n"/>
-      <c r="U14" s="12" t="n"/>
-      <c r="V14" s="13" t="n"/>
-      <c r="W14" s="12" t="n"/>
-      <c r="X14" s="13" t="n"/>
+      <c r="O14" s="14" t="n"/>
+      <c r="P14" s="12" t="n"/>
+      <c r="Q14" s="14" t="n"/>
+      <c r="R14" s="12" t="n"/>
+      <c r="S14" s="13" t="n"/>
+      <c r="T14" s="13" t="n"/>
+      <c r="U14" s="13" t="n"/>
+      <c r="V14" s="14" t="n"/>
+      <c r="W14" s="13" t="n"/>
+      <c r="X14" s="14" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>GE0003040        999 購入
 ステラロース200（大宮糧食）</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="11" t="inlineStr">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="12" t="inlineStr">
         <is>
           <t>0.2795</t>
         </is>
       </c>
-      <c r="M15" s="13" t="n"/>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="M15" s="14" t="n"/>
+      <c r="N15" s="12" t="inlineStr">
         <is>
           <t>1.12
 kg</t>
         </is>
       </c>
-      <c r="O15" s="13" t="n"/>
-      <c r="P15" s="11" t="n"/>
-      <c r="Q15" s="13" t="n"/>
-      <c r="R15" s="11" t="n"/>
-      <c r="S15" s="12" t="n"/>
-      <c r="T15" s="12" t="n"/>
-      <c r="U15" s="12" t="n"/>
-      <c r="V15" s="13" t="n"/>
-      <c r="W15" s="12" t="n"/>
-      <c r="X15" s="13" t="n"/>
+      <c r="O15" s="14" t="n"/>
+      <c r="P15" s="12" t="n"/>
+      <c r="Q15" s="14" t="n"/>
+      <c r="R15" s="12" t="n"/>
+      <c r="S15" s="13" t="n"/>
+      <c r="T15" s="13" t="n"/>
+      <c r="U15" s="13" t="n"/>
+      <c r="V15" s="14" t="n"/>
+      <c r="W15" s="13" t="n"/>
+      <c r="X15" s="14" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>GE0002070        999 購入
-ソレック K-EML</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="13" t="n"/>
-      <c r="L16" s="11" t="inlineStr">
+アレック K-EML</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="13" t="n"/>
+      <c r="J16" s="13" t="n"/>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>0.2995</t>
         </is>
       </c>
-      <c r="M16" s="13" t="n"/>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="12" t="inlineStr">
         <is>
           <t>1.20
 kg</t>
         </is>
       </c>
-      <c r="O16" s="13" t="n"/>
-      <c r="P16" s="11" t="n"/>
-      <c r="Q16" s="13" t="n"/>
-      <c r="R16" s="11" t="n"/>
-      <c r="S16" s="12" t="n"/>
-      <c r="T16" s="12" t="n"/>
-      <c r="U16" s="12" t="n"/>
-      <c r="V16" s="13" t="n"/>
-      <c r="W16" s="12" t="n"/>
-      <c r="X16" s="13" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="12" t="n"/>
+      <c r="Q16" s="14" t="n"/>
+      <c r="R16" s="12" t="n"/>
+      <c r="S16" s="13" t="n"/>
+      <c r="T16" s="13" t="n"/>
+      <c r="U16" s="13" t="n"/>
+      <c r="V16" s="14" t="n"/>
+      <c r="W16" s="13" t="n"/>
+      <c r="X16" s="14" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>GE0003110        999 購入
-ポエムＺＬ－３</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="11" t="inlineStr">
+ポエムZ L－3</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="13" t="n"/>
+      <c r="J17" s="13" t="n"/>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="12" t="inlineStr">
         <is>
           <t>0.4991</t>
         </is>
       </c>
-      <c r="M17" s="13" t="n"/>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="12" t="inlineStr">
         <is>
           <t>2.00
 kg</t>
         </is>
       </c>
-      <c r="O17" s="13" t="n"/>
-      <c r="P17" s="11" t="n"/>
-      <c r="Q17" s="13" t="n"/>
-      <c r="R17" s="11" t="n"/>
-      <c r="S17" s="12" t="n"/>
-      <c r="T17" s="12" t="n"/>
-      <c r="U17" s="12" t="n"/>
-      <c r="V17" s="13" t="n"/>
-      <c r="W17" s="12" t="n"/>
-      <c r="X17" s="13" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="12" t="n"/>
+      <c r="Q17" s="14" t="n"/>
+      <c r="R17" s="12" t="n"/>
+      <c r="S17" s="13" t="n"/>
+      <c r="T17" s="13" t="n"/>
+      <c r="U17" s="13" t="n"/>
+      <c r="V17" s="14" t="n"/>
+      <c r="W17" s="13" t="n"/>
+      <c r="X17" s="14" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>GE0006810        999 購入
 バクダードミルクコーヒー SSH-181</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="13" t="n"/>
-      <c r="L18" s="11" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="13" t="n"/>
+      <c r="J18" s="13" t="n"/>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="12" t="inlineStr">
         <is>
           <t>0.4991</t>
         </is>
       </c>
-      <c r="M18" s="13" t="n"/>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="12" t="inlineStr">
         <is>
           <t>2.00
 kg</t>
         </is>
       </c>
-      <c r="O18" s="13" t="n"/>
-      <c r="P18" s="11" t="n"/>
-      <c r="Q18" s="13" t="n"/>
-      <c r="R18" s="11" t="n"/>
-      <c r="S18" s="12" t="n"/>
-      <c r="T18" s="12" t="n"/>
-      <c r="U18" s="12" t="n"/>
-      <c r="V18" s="13" t="n"/>
-      <c r="W18" s="12" t="n"/>
-      <c r="X18" s="13" t="n"/>
+      <c r="O18" s="14" t="n"/>
+      <c r="P18" s="12" t="n"/>
+      <c r="Q18" s="14" t="n"/>
+      <c r="R18" s="12" t="n"/>
+      <c r="S18" s="13" t="n"/>
+      <c r="T18" s="13" t="n"/>
+      <c r="U18" s="13" t="n"/>
+      <c r="V18" s="14" t="n"/>
+      <c r="W18" s="13" t="n"/>
+      <c r="X18" s="14" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>GE0004800        999 購入
 コーヒーパウダーフレーバー YM-5309</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="11" t="inlineStr">
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="13" t="n"/>
+      <c r="K19" s="14" t="n"/>
+      <c r="L19" s="12" t="inlineStr">
         <is>
           <t>0.2995</t>
         </is>
       </c>
-      <c r="M19" s="13" t="n"/>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="M19" s="14" t="n"/>
+      <c r="N19" s="12" t="inlineStr">
         <is>
           <t>1.20
 kg</t>
         </is>
       </c>
-      <c r="O19" s="13" t="n"/>
-      <c r="P19" s="11" t="n"/>
-      <c r="Q19" s="13" t="n"/>
-      <c r="R19" s="11" t="n"/>
-      <c r="S19" s="12" t="n"/>
-      <c r="T19" s="12" t="n"/>
-      <c r="U19" s="12" t="n"/>
-      <c r="V19" s="13" t="n"/>
-      <c r="W19" s="12" t="n"/>
-      <c r="X19" s="13" t="n"/>
+      <c r="O19" s="14" t="n"/>
+      <c r="P19" s="12" t="n"/>
+      <c r="Q19" s="14" t="n"/>
+      <c r="R19" s="12" t="n"/>
+      <c r="S19" s="13" t="n"/>
+      <c r="T19" s="13" t="n"/>
+      <c r="U19" s="13" t="n"/>
+      <c r="V19" s="14" t="n"/>
+      <c r="W19" s="13" t="n"/>
+      <c r="X19" s="14" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="29" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
-      <c r="K20" s="13" t="n"/>
-      <c r="L20" s="11" t="n"/>
-      <c r="M20" s="13" t="n"/>
-      <c r="N20" s="11" t="n"/>
-      <c r="O20" s="13" t="n"/>
-      <c r="P20" s="11" t="n"/>
-      <c r="Q20" s="13" t="n"/>
-      <c r="R20" s="11" t="n"/>
-      <c r="S20" s="12" t="n"/>
-      <c r="T20" s="12" t="n"/>
-      <c r="U20" s="12" t="n"/>
-      <c r="V20" s="13" t="n"/>
-      <c r="W20" s="12" t="n"/>
-      <c r="X20" s="13" t="n"/>
+      <c r="A20" s="30" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="13" t="n"/>
+      <c r="J20" s="13" t="n"/>
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="14" t="n"/>
+      <c r="P20" s="12" t="n"/>
+      <c r="Q20" s="14" t="n"/>
+      <c r="R20" s="12" t="n"/>
+      <c r="S20" s="13" t="n"/>
+      <c r="T20" s="13" t="n"/>
+      <c r="U20" s="13" t="n"/>
+      <c r="V20" s="14" t="n"/>
+      <c r="W20" s="13" t="n"/>
+      <c r="X20" s="14" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
-      <c r="K21" s="13" t="n"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="13" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="13" t="n"/>
-      <c r="P21" s="11" t="n"/>
-      <c r="Q21" s="13" t="n"/>
-      <c r="R21" s="11" t="n"/>
-      <c r="S21" s="12" t="n"/>
-      <c r="T21" s="12" t="n"/>
-      <c r="U21" s="12" t="n"/>
-      <c r="V21" s="13" t="n"/>
-      <c r="W21" s="12" t="n"/>
-      <c r="X21" s="13" t="n"/>
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="13" t="n"/>
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="14" t="n"/>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="14" t="n"/>
+      <c r="P21" s="12" t="n"/>
+      <c r="Q21" s="14" t="n"/>
+      <c r="R21" s="12" t="n"/>
+      <c r="S21" s="13" t="n"/>
+      <c r="T21" s="13" t="n"/>
+      <c r="U21" s="13" t="n"/>
+      <c r="V21" s="14" t="n"/>
+      <c r="W21" s="13" t="n"/>
+      <c r="X21" s="14" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="29" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
-      <c r="K22" s="13" t="n"/>
-      <c r="L22" s="11" t="n"/>
-      <c r="M22" s="13" t="n"/>
-      <c r="N22" s="11" t="n"/>
-      <c r="O22" s="13" t="n"/>
-      <c r="P22" s="11" t="n"/>
-      <c r="Q22" s="13" t="n"/>
-      <c r="R22" s="11" t="n"/>
-      <c r="S22" s="12" t="n"/>
-      <c r="T22" s="12" t="n"/>
-      <c r="U22" s="12" t="n"/>
-      <c r="V22" s="13" t="n"/>
-      <c r="W22" s="12" t="n"/>
-      <c r="X22" s="13" t="n"/>
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="13" t="n"/>
+      <c r="I22" s="13" t="n"/>
+      <c r="J22" s="13" t="n"/>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="14" t="n"/>
+      <c r="N22" s="12" t="n"/>
+      <c r="O22" s="14" t="n"/>
+      <c r="P22" s="12" t="n"/>
+      <c r="Q22" s="14" t="n"/>
+      <c r="R22" s="12" t="n"/>
+      <c r="S22" s="13" t="n"/>
+      <c r="T22" s="13" t="n"/>
+      <c r="U22" s="13" t="n"/>
+      <c r="V22" s="14" t="n"/>
+      <c r="W22" s="13" t="n"/>
+      <c r="X22" s="14" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="13" t="n"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="13" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="13" t="n"/>
-      <c r="P23" s="11" t="n"/>
-      <c r="Q23" s="13" t="n"/>
-      <c r="R23" s="11" t="n"/>
-      <c r="S23" s="12" t="n"/>
-      <c r="T23" s="12" t="n"/>
-      <c r="U23" s="12" t="n"/>
-      <c r="V23" s="13" t="n"/>
-      <c r="W23" s="12" t="n"/>
-      <c r="X23" s="13" t="n"/>
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="13" t="n"/>
+      <c r="J23" s="13" t="n"/>
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="14" t="n"/>
+      <c r="N23" s="12" t="n"/>
+      <c r="O23" s="14" t="n"/>
+      <c r="P23" s="12" t="n"/>
+      <c r="Q23" s="14" t="n"/>
+      <c r="R23" s="12" t="n"/>
+      <c r="S23" s="13" t="n"/>
+      <c r="T23" s="13" t="n"/>
+      <c r="U23" s="13" t="n"/>
+      <c r="V23" s="14" t="n"/>
+      <c r="W23" s="13" t="n"/>
+      <c r="X23" s="14" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="29" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="13" t="n"/>
-      <c r="L24" s="11" t="n"/>
-      <c r="M24" s="13" t="n"/>
-      <c r="N24" s="11" t="n"/>
-      <c r="O24" s="13" t="n"/>
-      <c r="P24" s="11" t="n"/>
-      <c r="Q24" s="13" t="n"/>
-      <c r="R24" s="11" t="n"/>
-      <c r="S24" s="12" t="n"/>
-      <c r="T24" s="12" t="n"/>
-      <c r="U24" s="12" t="n"/>
-      <c r="V24" s="13" t="n"/>
-      <c r="W24" s="12" t="n"/>
-      <c r="X24" s="13" t="n"/>
+      <c r="A24" s="30" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="13" t="n"/>
+      <c r="I24" s="13" t="n"/>
+      <c r="J24" s="13" t="n"/>
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="14" t="n"/>
+      <c r="N24" s="12" t="n"/>
+      <c r="O24" s="14" t="n"/>
+      <c r="P24" s="12" t="n"/>
+      <c r="Q24" s="14" t="n"/>
+      <c r="R24" s="12" t="n"/>
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="13" t="n"/>
+      <c r="U24" s="13" t="n"/>
+      <c r="V24" s="14" t="n"/>
+      <c r="W24" s="13" t="n"/>
+      <c r="X24" s="14" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="13" t="n"/>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="13" t="n"/>
-      <c r="N25" s="11" t="n"/>
-      <c r="O25" s="13" t="n"/>
-      <c r="P25" s="11" t="n"/>
-      <c r="Q25" s="13" t="n"/>
-      <c r="R25" s="11" t="n"/>
-      <c r="S25" s="12" t="n"/>
-      <c r="T25" s="12" t="n"/>
-      <c r="U25" s="12" t="n"/>
-      <c r="V25" s="13" t="n"/>
-      <c r="W25" s="12" t="n"/>
-      <c r="X25" s="13" t="n"/>
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="14" t="n"/>
+      <c r="N25" s="12" t="n"/>
+      <c r="O25" s="14" t="n"/>
+      <c r="P25" s="12" t="n"/>
+      <c r="Q25" s="14" t="n"/>
+      <c r="R25" s="12" t="n"/>
+      <c r="S25" s="13" t="n"/>
+      <c r="T25" s="13" t="n"/>
+      <c r="U25" s="13" t="n"/>
+      <c r="V25" s="14" t="n"/>
+      <c r="W25" s="13" t="n"/>
+      <c r="X25" s="14" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="29" t="n"/>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="13" t="n"/>
-      <c r="L26" s="11" t="n"/>
-      <c r="M26" s="13" t="n"/>
-      <c r="N26" s="11" t="n"/>
-      <c r="O26" s="13" t="n"/>
-      <c r="P26" s="11" t="n"/>
-      <c r="Q26" s="13" t="n"/>
-      <c r="R26" s="11" t="n"/>
-      <c r="S26" s="12" t="n"/>
-      <c r="T26" s="12" t="n"/>
-      <c r="U26" s="12" t="n"/>
-      <c r="V26" s="13" t="n"/>
-      <c r="W26" s="12" t="n"/>
-      <c r="X26" s="13" t="n"/>
+      <c r="A26" s="30" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="13" t="n"/>
+      <c r="G26" s="13" t="n"/>
+      <c r="H26" s="13" t="n"/>
+      <c r="I26" s="13" t="n"/>
+      <c r="J26" s="13" t="n"/>
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="14" t="n"/>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="14" t="n"/>
+      <c r="P26" s="12" t="n"/>
+      <c r="Q26" s="14" t="n"/>
+      <c r="R26" s="12" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="13" t="n"/>
+      <c r="U26" s="13" t="n"/>
+      <c r="V26" s="14" t="n"/>
+      <c r="W26" s="13" t="n"/>
+      <c r="X26" s="14" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="13" t="n"/>
-      <c r="L27" s="11" t="n"/>
-      <c r="M27" s="13" t="n"/>
-      <c r="N27" s="11" t="n"/>
-      <c r="O27" s="13" t="n"/>
-      <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="13" t="n"/>
-      <c r="R27" s="11" t="n"/>
-      <c r="S27" s="12" t="n"/>
-      <c r="T27" s="12" t="n"/>
-      <c r="U27" s="12" t="n"/>
-      <c r="V27" s="13" t="n"/>
-      <c r="W27" s="12" t="n"/>
-      <c r="X27" s="13" t="n"/>
+      <c r="A27" s="30" t="n"/>
+      <c r="B27" s="13" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="13" t="n"/>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="14" t="n"/>
+      <c r="N27" s="12" t="n"/>
+      <c r="O27" s="14" t="n"/>
+      <c r="P27" s="12" t="n"/>
+      <c r="Q27" s="14" t="n"/>
+      <c r="R27" s="12" t="n"/>
+      <c r="S27" s="13" t="n"/>
+      <c r="T27" s="13" t="n"/>
+      <c r="U27" s="13" t="n"/>
+      <c r="V27" s="14" t="n"/>
+      <c r="W27" s="13" t="n"/>
+      <c r="X27" s="14" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="29" t="n"/>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="13" t="n"/>
-      <c r="L28" s="11" t="n"/>
-      <c r="M28" s="13" t="n"/>
-      <c r="N28" s="11" t="n"/>
-      <c r="O28" s="13" t="n"/>
-      <c r="P28" s="11" t="n"/>
-      <c r="Q28" s="13" t="n"/>
-      <c r="R28" s="11" t="n"/>
-      <c r="S28" s="12" t="n"/>
-      <c r="T28" s="12" t="n"/>
-      <c r="U28" s="12" t="n"/>
-      <c r="V28" s="13" t="n"/>
-      <c r="W28" s="12" t="n"/>
-      <c r="X28" s="13" t="n"/>
+      <c r="A28" s="30" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="13" t="n"/>
+      <c r="J28" s="13" t="n"/>
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="14" t="n"/>
+      <c r="N28" s="12" t="n"/>
+      <c r="O28" s="14" t="n"/>
+      <c r="P28" s="12" t="n"/>
+      <c r="Q28" s="14" t="n"/>
+      <c r="R28" s="12" t="n"/>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="13" t="n"/>
+      <c r="U28" s="13" t="n"/>
+      <c r="V28" s="14" t="n"/>
+      <c r="W28" s="13" t="n"/>
+      <c r="X28" s="14" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="29" t="n"/>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="13" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="13" t="n"/>
-      <c r="N29" s="11" t="n"/>
-      <c r="O29" s="13" t="n"/>
-      <c r="P29" s="11" t="n"/>
-      <c r="Q29" s="13" t="n"/>
-      <c r="R29" s="11" t="n"/>
-      <c r="S29" s="12" t="n"/>
-      <c r="T29" s="12" t="n"/>
-      <c r="U29" s="12" t="n"/>
-      <c r="V29" s="13" t="n"/>
-      <c r="W29" s="12" t="n"/>
-      <c r="X29" s="13" t="n"/>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A29" s="30" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="13" t="n"/>
+      <c r="I29" s="13" t="n"/>
+      <c r="J29" s="13" t="n"/>
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="14" t="n"/>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="14" t="n"/>
+      <c r="P29" s="12" t="n"/>
+      <c r="Q29" s="14" t="n"/>
+      <c r="R29" s="12" t="n"/>
+      <c r="S29" s="13" t="n"/>
+      <c r="T29" s="13" t="n"/>
+      <c r="U29" s="13" t="n"/>
+      <c r="V29" s="14" t="n"/>
+      <c r="W29" s="13" t="n"/>
+      <c r="X29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="30" t="n"/>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="13" t="n"/>
+      <c r="J30" s="13" t="n"/>
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="14" t="n"/>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="14" t="n"/>
+      <c r="P30" s="12" t="n"/>
+      <c r="Q30" s="14" t="n"/>
+      <c r="R30" s="12" t="n"/>
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="13" t="n"/>
+      <c r="U30" s="13" t="n"/>
+      <c r="V30" s="14" t="n"/>
+      <c r="W30" s="13" t="n"/>
+      <c r="X30" s="14" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="13" t="n"/>
+      <c r="I31" s="13" t="n"/>
+      <c r="J31" s="13" t="n"/>
+      <c r="K31" s="14" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="14" t="n"/>
+      <c r="N31" s="12" t="n"/>
+      <c r="O31" s="14" t="n"/>
+      <c r="P31" s="12" t="n"/>
+      <c r="Q31" s="14" t="n"/>
+      <c r="R31" s="12" t="n"/>
+      <c r="S31" s="13" t="n"/>
+      <c r="T31" s="13" t="n"/>
+      <c r="U31" s="13" t="n"/>
+      <c r="V31" s="14" t="n"/>
+      <c r="W31" s="13" t="n"/>
+      <c r="X31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="B30" s="31" t="n"/>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="31" t="n"/>
-      <c r="H30" s="31" t="n"/>
-      <c r="I30" s="31" t="n"/>
-      <c r="J30" s="31" t="n"/>
-      <c r="K30" s="31" t="n"/>
-      <c r="L30" s="31" t="n"/>
-      <c r="M30" s="31" t="n"/>
-      <c r="N30" s="31" t="n"/>
-      <c r="O30" s="31" t="n"/>
-      <c r="P30" s="31" t="n"/>
-      <c r="Q30" s="31" t="n"/>
-      <c r="R30" s="31" t="n"/>
-      <c r="S30" s="31" t="n"/>
-      <c r="T30" s="31" t="n"/>
-      <c r="U30" s="31" t="n"/>
-      <c r="V30" s="31" t="n"/>
-      <c r="W30" s="31" t="n"/>
-      <c r="X30" s="32" t="n"/>
+      <c r="B32" s="32" t="n"/>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="32" t="n"/>
+      <c r="E32" s="32" t="n"/>
+      <c r="F32" s="32" t="n"/>
+      <c r="G32" s="32" t="n"/>
+      <c r="H32" s="32" t="n"/>
+      <c r="I32" s="32" t="n"/>
+      <c r="J32" s="32" t="n"/>
+      <c r="K32" s="32" t="n"/>
+      <c r="L32" s="32" t="n"/>
+      <c r="M32" s="32" t="n"/>
+      <c r="N32" s="32" t="n"/>
+      <c r="O32" s="32" t="n"/>
+      <c r="P32" s="32" t="n"/>
+      <c r="Q32" s="32" t="n"/>
+      <c r="R32" s="32" t="n"/>
+      <c r="S32" s="32" t="n"/>
+      <c r="T32" s="32" t="n"/>
+      <c r="U32" s="32" t="n"/>
+      <c r="V32" s="32" t="n"/>
+      <c r="W32" s="32" t="n"/>
+      <c r="X32" s="33" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="145">
+  <mergeCells count="157">
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="N20:O20"/>
     <mergeCell ref="P20:Q20"/>
@@ -1750,11 +1809,11 @@
     <mergeCell ref="W26:X26"/>
     <mergeCell ref="N12:O12"/>
     <mergeCell ref="R16:V16"/>
-    <mergeCell ref="D2:H2"/>
     <mergeCell ref="R25:V25"/>
     <mergeCell ref="R8:X8"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A10:K11"/>
+    <mergeCell ref="A32:X32"/>
     <mergeCell ref="L14:M14"/>
     <mergeCell ref="W10:X11"/>
     <mergeCell ref="N14:O14"/>
@@ -1767,7 +1826,9 @@
     <mergeCell ref="P13:Q13"/>
     <mergeCell ref="D4:N4"/>
     <mergeCell ref="R22:V22"/>
+    <mergeCell ref="L31:M31"/>
     <mergeCell ref="A17:K17"/>
+    <mergeCell ref="N31:O31"/>
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="L21:M21"/>
     <mergeCell ref="N15:O15"/>
@@ -1778,13 +1839,14 @@
     <mergeCell ref="A19:K19"/>
     <mergeCell ref="A28:K28"/>
     <mergeCell ref="W14:X14"/>
-    <mergeCell ref="K2:N2"/>
     <mergeCell ref="W28:X28"/>
     <mergeCell ref="R14:V14"/>
     <mergeCell ref="R23:V23"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="O5:Q5"/>
     <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="P2:X2"/>
     <mergeCell ref="L16:M16"/>
     <mergeCell ref="N16:O16"/>
     <mergeCell ref="L10:M11"/>
@@ -1792,8 +1854,10 @@
     <mergeCell ref="N10:O11"/>
     <mergeCell ref="P25:Q25"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="L2:O2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="R27:V27"/>
+    <mergeCell ref="L30:M30"/>
     <mergeCell ref="W16:X16"/>
     <mergeCell ref="A26:K26"/>
     <mergeCell ref="L20:M20"/>
@@ -1806,12 +1870,12 @@
     <mergeCell ref="R17:V17"/>
     <mergeCell ref="L22:M22"/>
     <mergeCell ref="W27:X27"/>
-    <mergeCell ref="A30:X30"/>
+    <mergeCell ref="N30:O30"/>
     <mergeCell ref="W17:X17"/>
+    <mergeCell ref="P30:Q30"/>
     <mergeCell ref="P14:Q14"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="W19:X19"/>
-    <mergeCell ref="I2:J2"/>
     <mergeCell ref="W25:X25"/>
     <mergeCell ref="R29:V29"/>
     <mergeCell ref="K5:L5"/>
@@ -1819,6 +1883,8 @@
     <mergeCell ref="R13:V13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="W30:X30"/>
+    <mergeCell ref="R31:V31"/>
     <mergeCell ref="W20:X20"/>
     <mergeCell ref="R5:X5"/>
     <mergeCell ref="L24:M24"/>
@@ -1829,6 +1895,7 @@
     <mergeCell ref="N27:O27"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="W22:X22"/>
+    <mergeCell ref="W31:X31"/>
     <mergeCell ref="N17:O17"/>
     <mergeCell ref="R21:V21"/>
     <mergeCell ref="L26:M26"/>
@@ -1843,19 +1910,22 @@
     <mergeCell ref="N19:O19"/>
     <mergeCell ref="P19:Q19"/>
     <mergeCell ref="A14:K14"/>
+    <mergeCell ref="D2:G2"/>
     <mergeCell ref="R10:V11"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="A9:X9"/>
     <mergeCell ref="O6:Q6"/>
     <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="P29:Q29"/>
     <mergeCell ref="R19:V19"/>
-    <mergeCell ref="O2:X2"/>
     <mergeCell ref="R28:V28"/>
+    <mergeCell ref="P31:Q31"/>
     <mergeCell ref="L13:M13"/>
     <mergeCell ref="N21:O21"/>
     <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="R30:V30"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="L15:M15"/>
@@ -1877,6 +1947,7 @@
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="R18:V18"/>
     <mergeCell ref="W13:X13"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/IMG_9688.xlsx
+++ b/output/IMG_9688.xlsx
@@ -1130,7 +1130,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>GE0006280        999 購入
+          <t>GE0006280
 Wheyco W80-パフォーマンスアカデミー</t>
         </is>
       </c>
@@ -1146,7 +1146,8 @@
       <c r="K12" s="28" t="n"/>
       <c r="L12" s="29" t="inlineStr">
         <is>
-          <t>89.8383</t>
+          <t>999 購入
+89.8383</t>
         </is>
       </c>
       <c r="M12" s="28" t="n"/>
@@ -1170,7 +1171,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>GE0005150        999 購入
+          <t>GE0005150
 TATA INSTANT COFFEE FR-2132（深煎り）</t>
         </is>
       </c>
@@ -1186,7 +1187,8 @@
       <c r="K13" s="14" t="n"/>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>5.9893</t>
+          <t>999 購入
+5.9893</t>
         </is>
       </c>
       <c r="M13" s="14" t="n"/>
@@ -1210,7 +1212,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>GE0004220        999 購入
+          <t>GE0004220
 練乳パウダー</t>
         </is>
       </c>
@@ -1226,7 +1228,8 @@
       <c r="K14" s="14" t="n"/>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>2.2959</t>
+          <t>999 購入
+2.2959</t>
         </is>
       </c>
       <c r="M14" s="14" t="n"/>
@@ -1250,8 +1253,8 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>GE0003040        999 購入
-ステラロース200（大宮糧食）</t>
+          <t>GE0003040
+スタラース200（大宮糧食）</t>
         </is>
       </c>
       <c r="B15" s="13" t="n"/>
@@ -1266,7 +1269,8 @@
       <c r="K15" s="14" t="n"/>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>0.2795</t>
+          <t>999 購入
+0.2795</t>
         </is>
       </c>
       <c r="M15" s="14" t="n"/>
@@ -1290,7 +1294,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>GE0002070        999 購入
+          <t>GE0002070
 アレック K-EML</t>
         </is>
       </c>
@@ -1306,7 +1310,8 @@
       <c r="K16" s="14" t="n"/>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>0.2995</t>
+          <t>999 購入
+0.2995</t>
         </is>
       </c>
       <c r="M16" s="14" t="n"/>
@@ -1330,8 +1335,8 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>GE0003110        999 購入
-ポエムZ L－3</t>
+          <t>GE0003110
+ポエムＺＬ－３</t>
         </is>
       </c>
       <c r="B17" s="13" t="n"/>
@@ -1346,7 +1351,8 @@
       <c r="K17" s="14" t="n"/>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>0.4991</t>
+          <t>999 購入
+0.4991</t>
         </is>
       </c>
       <c r="M17" s="14" t="n"/>
@@ -1370,8 +1376,8 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>GE0006810        999 購入
-バクダードミルクコーヒー SSH-181</t>
+          <t>GE0006810
+パウダートミルクコーヒー SSH-181</t>
         </is>
       </c>
       <c r="B18" s="13" t="n"/>
@@ -1386,7 +1392,8 @@
       <c r="K18" s="14" t="n"/>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>0.4991</t>
+          <t>999 購入
+0.4991</t>
         </is>
       </c>
       <c r="M18" s="14" t="n"/>
@@ -1410,7 +1417,7 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>GE0004800        999 購入
+          <t>GE0004800
 コーヒーパウダーフレーバー YM-5309</t>
         </is>
       </c>
@@ -1426,7 +1433,8 @@
       <c r="K19" s="14" t="n"/>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>0.2995</t>
+          <t>999 購入
+0.2995</t>
         </is>
       </c>
       <c r="M19" s="14" t="n"/>

--- a/output/IMG_9688.xlsx
+++ b/output/IMG_9688.xlsx
@@ -583,9 +583,17 @@
         </is>
       </c>
       <c r="B2" s="5" t="n"/>
-      <c r="C2" s="2" t="n"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>0000056481</t>
+        </is>
+      </c>
       <c r="D2" s="5" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F2" s="5" t="n"/>
       <c r="G2" s="7" t="inlineStr">
         <is>
@@ -593,7 +601,11 @@
         </is>
       </c>
       <c r="H2" s="5" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2018/12/05</t>
+        </is>
+      </c>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
@@ -607,7 +619,11 @@
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
-      <c r="C3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>S00000200 製造１課　倉庫</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
@@ -619,7 +635,11 @@
         </is>
       </c>
       <c r="J3" s="5" t="n"/>
-      <c r="K3" s="2" t="n"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>2018/12/14</t>
+        </is>
+      </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="7" t="inlineStr">
         <is>
@@ -635,7 +655,11 @@
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>HA0002610</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="7" t="inlineStr">
@@ -643,7 +667,11 @@
           <t>工順</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -651,7 +679,11 @@
         </is>
       </c>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="2" t="n"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>400.72 kg</t>
+        </is>
+      </c>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="5" t="n"/>
@@ -663,7 +695,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
+        </is>
+      </c>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
@@ -675,7 +711,11 @@
         </is>
       </c>
       <c r="J5" s="5" t="n"/>
-      <c r="K5" s="2" t="n"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0000051090</t>
+        </is>
+      </c>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="5" t="n"/>
@@ -687,7 +727,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="2" t="n"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
@@ -699,7 +743,11 @@
         </is>
       </c>
       <c r="J6" s="5" t="n"/>
-      <c r="K6" s="2" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>S00000200 製造１課　倉庫</t>
+        </is>
+      </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
       <c r="N6" s="5" t="n"/>
@@ -793,13 +841,28 @@
       <c r="N9" s="5" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="8" t="n"/>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>GE0006280
+Wheyco W80-パフォーマンスアカデミー
+999 購入</t>
+        </is>
+      </c>
       <c r="B10" s="4" t="n"/>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="5" t="n"/>
-      <c r="E10" s="8" t="n"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>89.8383</t>
+        </is>
+      </c>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>360.00
+kg</t>
+        </is>
+      </c>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="5" t="n"/>
@@ -809,13 +872,28 @@
       <c r="N10" s="5" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="n"/>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>GE0005150
+TATA INSTANT COFFEE FR-2132（深煎り）
+999 購入</t>
+        </is>
+      </c>
       <c r="B11" s="4" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="5" t="n"/>
-      <c r="E11" s="8" t="n"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>5.9893</t>
+        </is>
+      </c>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="8" t="n"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>24.00
+kg</t>
+        </is>
+      </c>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="5" t="n"/>
@@ -825,13 +903,28 @@
       <c r="N11" s="5" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="n"/>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>GE0004220
+練乳パウダー
+999 購入</t>
+        </is>
+      </c>
       <c r="B12" s="4" t="n"/>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="5" t="n"/>
-      <c r="E12" s="8" t="n"/>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2.2959</t>
+        </is>
+      </c>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>9.20
+kg</t>
+        </is>
+      </c>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="5" t="n"/>
@@ -841,13 +934,28 @@
       <c r="N12" s="5" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="n"/>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>GE0003040
+ステラロース200（大宮糧食）
+999 購入</t>
+        </is>
+      </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="5" t="n"/>
-      <c r="E13" s="8" t="n"/>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>0.2795</t>
+        </is>
+      </c>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="8" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>1.12
+kg</t>
+        </is>
+      </c>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="8" t="n"/>
       <c r="J13" s="5" t="n"/>
@@ -857,13 +965,28 @@
       <c r="N13" s="5" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="n"/>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>GE0002070
+ソレック K-EML
+999 購入</t>
+        </is>
+      </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="5" t="n"/>
-      <c r="E14" s="8" t="n"/>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>0.2995</t>
+        </is>
+      </c>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>1.20
+kg</t>
+        </is>
+      </c>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="5" t="n"/>
@@ -873,13 +996,28 @@
       <c r="N14" s="5" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="8" t="n"/>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>GE0003110
+ポエムZ L－3
+999 購入</t>
+        </is>
+      </c>
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="5" t="n"/>
-      <c r="E15" s="8" t="n"/>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>0.4991</t>
+        </is>
+      </c>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="8" t="n"/>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>2.00
+kg</t>
+        </is>
+      </c>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="5" t="n"/>
@@ -889,13 +1027,28 @@
       <c r="N15" s="5" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="n"/>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>GE0006810
+バクダードミルクコーヒー SSH-181
+999 購入</t>
+        </is>
+      </c>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="8" t="n"/>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>0.4991</t>
+        </is>
+      </c>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>2.00
+kg</t>
+        </is>
+      </c>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="5" t="n"/>
@@ -905,13 +1058,28 @@
       <c r="N16" s="5" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="n"/>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>GE0004800
+コーヒーパウダーフレーバー YM-5309
+999 購入</t>
+        </is>
+      </c>
       <c r="B17" s="4" t="n"/>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="8" t="n"/>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>0.2995</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="8" t="n"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>1.20
+kg</t>
+        </is>
+      </c>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="8" t="n"/>
       <c r="J17" s="5" t="n"/>

--- a/output/IMG_9688.xlsx
+++ b/output/IMG_9688.xlsx
@@ -38,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -47,13 +47,13 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
       <left style="thin"/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin"/>
       <bottom style="thin"/>
@@ -86,32 +86,56 @@
     </border>
     <border>
       <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin"/>
       <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin"/>
+      <left style="thin"/>
+      <right/>
       <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
     </border>
     <border>
       <left style="thin"/>
-      <right style="thin"/>
+      <right/>
       <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
       <right style="thin"/>
       <top/>
       <bottom style="thin"/>
@@ -124,6 +148,46 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top/>
@@ -137,36 +201,31 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -533,19 +592,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6.25" customWidth="1" min="1" max="1"/>
-    <col width="14.58333333333333" customWidth="1" min="2" max="2"/>
-    <col width="10.41666666666667" customWidth="1" min="3" max="3"/>
-    <col width="6.25" customWidth="1" min="4" max="4"/>
-    <col width="10.41666666666667" customWidth="1" min="5" max="5"/>
-    <col width="8.5" customWidth="1" min="6" max="6"/>
-    <col width="10.41666666666667" customWidth="1" min="7" max="7"/>
-    <col width="10.41666666666667" customWidth="1" min="8" max="8"/>
-    <col width="14.58333333333333" customWidth="1" min="9" max="9"/>
-    <col width="10.41666666666667" customWidth="1" min="10" max="10"/>
+    <col width="7.579462102689487" customWidth="1" min="1" max="1"/>
+    <col width="13.6919315403423" customWidth="1" min="2" max="2"/>
+    <col width="7.823960880195599" customWidth="1" min="3" max="3"/>
+    <col width="5.867970660146699" customWidth="1" min="4" max="4"/>
+    <col width="7.823960880195599" customWidth="1" min="5" max="5"/>
+    <col width="5.867970660146699" customWidth="1" min="6" max="6"/>
+    <col width="9.779951100244498" customWidth="1" min="7" max="7"/>
+    <col width="9.779951100244498" customWidth="1" min="8" max="8"/>
+    <col width="8.312958435207824" customWidth="1" min="9" max="9"/>
+    <col width="13.6919315403423" customWidth="1" min="10" max="10"/>
+    <col width="9.779951100244498" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -554,521 +614,608 @@
           <t>製造指図書</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="4" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>手配No.</t>
+        </is>
+      </c>
       <c r="B2" s="3" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>0000056481</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>作成者</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="n"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>手配先</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>S00000200 製造１課　倉庫</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>手配納期</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>品目CD</t>
+        </is>
+      </c>
       <c r="B4" s="3" t="n"/>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>HA0002610</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>工順</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>発注手配数</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>品目名</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>クレイジーマックスプロテイン（カフェオレ風味）造粒品</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>製番</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>手配内容</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>20　　仕込</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>完成入庫</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
       <c r="I6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ロットNo.</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>完成日</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
       <c r="I7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
           <t>調合票</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="3" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>成分名</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>原単位</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>分量</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>秤量者</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>原料ロット</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>確認者</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>成分名</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>分量</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>秤量者</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>原料ロット</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t>確認者</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="11" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="2" t="n"/>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>GE0006280
+Wheyco W80-パフォーマンスアカデミー　999 購入</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="4" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>89.8383</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>360.00 kg</t>
+        </is>
+      </c>
       <c r="G11" s="3" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="3" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="4" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="2" t="n"/>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>GE0005150
+TATA INSTANT COFFEE FR-2132（深煎り）　999 購入</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="4" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>5.9893</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>24.00 kg</t>
+        </is>
+      </c>
       <c r="G12" s="3" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="3" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="4" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="2" t="n"/>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>GE0004220
+練乳パウダー　999 購入</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
       <c r="C13" s="3" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="4" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>2.2959</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>9.20 kg</t>
+        </is>
+      </c>
       <c r="G13" s="3" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="3" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="4" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="2" t="n"/>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>GE0003040
+ステラロース200（大宮糧食）　999 購入</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="4" t="n"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>0.2795</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1.12 kg</t>
+        </is>
+      </c>
       <c r="G14" s="3" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="3" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="4" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="2" t="n"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>GE0002070
+ソレック K-EML　999 購入</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
       <c r="C15" s="3" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="4" t="n"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>0.2995</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1.20 kg</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="3" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="4" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="2" t="n"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>GE0003110
+ポエムＺＬ－３　999 購入</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
       <c r="C16" s="3" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>0.4991</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>2.00 kg</t>
+        </is>
+      </c>
       <c r="G16" s="3" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="4" t="n"/>
-      <c r="B17" s="2" t="n"/>
+      <c r="B17" s="5" t="n"/>
       <c r="C17" s="3" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="3" t="n"/>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="3" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="3" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n"/>
-      <c r="B18" s="2" t="n"/>
+      <c r="B18" s="5" t="n"/>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="5" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="3" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="3" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="3" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="4" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="B19" s="5" t="n"/>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="5" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="3" t="n"/>
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="3" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="3" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="B20" s="5" t="n"/>
       <c r="C20" s="3" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="5" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="3" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="3" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="3" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="2" t="n"/>
+      <c r="B21" s="5" t="n"/>
       <c r="C21" s="3" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="5" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="3" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="3" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="3" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="5" t="n"/>
       <c r="C22" s="3" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="5" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="3" t="n"/>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="3" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="3" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="B23" s="5" t="n"/>
       <c r="C23" s="3" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="5" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="3" t="n"/>
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="3" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="3" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="B24" s="5" t="n"/>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="5" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="3" t="n"/>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="3" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="3" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="2" t="n"/>
+      <c r="B25" s="5" t="n"/>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="5" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="3" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="3" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="3" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="9" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="3" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
-      <c r="I26" s="3" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="3" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="3" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="3" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="3" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="3" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="3" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="3" t="n"/>
-    </row>
-    <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="3" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="91">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="F29:G29"/>
+  <mergeCells count="94">
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="H9:H10"/>
     <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H10:I10"/>
     <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I16:J16"/>
     <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I9:J10"/>
     <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A7:D7"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F5:G5"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="I24:J24"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="H5:I5"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="F4:G4"/>
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="A9:C10"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="H21:I21"/>
     <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="C26:K26"/>
     <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H30:I30"/>
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D21:E21"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I12:J12"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D16:E16"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="G4:H4"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
